--- a/results/Int Task Remove ACC 1.0/Rando_fi_all.xlsx
+++ b/results/Int Task Remove ACC 1.0/Rando_fi_all.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-0.0006385068762278734 +/- 0.0013900758053128556</t>
+          <t>0.00653241650294697 +/- 0.0009069835615235312</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -886,157 +886,157 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-0.0016699410609037125 +/- 0.0012269151273867347</t>
+          <t>0.004273084479371347 +/- 0.001977487439999751</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.0011296660117878 +/- 0.0008799839325721715</t>
+          <t>0.003143418467583492 +/- 0.0010349365179619606</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.004223968565815306 +/- 0.000962471411702602</t>
+          <t>-0.00034381139489194636 +/- 0.000933202357563846</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.00039292730844796563 +/- 0.0005289945783039786</t>
+          <t>0.0059430255402750706 +/- 0.0008633789701005311</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.002897838899803573 +/- 0.0010407475491364085</t>
+          <t>0.0018172888015717038 +/- 0.000583219159481226</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.00029469548133598256 +/- 0.00024061785292568027</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.006581532416502977 +/- 0.0018403726910800734</t>
+          <t>0.0055992141453831135 +/- 0.001357590860617412</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.00422396856581535 +/- 0.0017871714536994373</t>
+          <t>0.005844793713163076 +/- 0.002201467075738235</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.006925343811394924 +/- 0.00225559184738803</t>
+          <t>0.013948919449901776 +/- 0.0015869837349119327</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-0.0006385068762278622 +/- 0.0010077742892280572</t>
+          <t>-0.00019646365422395506 +/- 0.0011664383189624783</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.005648330058939133 +/- 0.001393542333900898</t>
+          <t>0.002111984282907675 +/- 0.0007934918674559685</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-0.002504911591355574 +/- 0.0011508226437976453</t>
+          <t>0.004273084479371347 +/- 0.0013549228118009515</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-0.015520628683693494 +/- 0.0019914670857282078</t>
+          <t>-0.013948919449901754 +/- 0.0016466654827347858</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-0.008104125736738677 +/- 0.002506836965653231</t>
+          <t>-0.0020137524557956588 +/- 0.0010861171113701507</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.00279960707269159 +/- 0.0012239622587796953</t>
+          <t>0.006139489194499037 +/- 0.0012080917363702338</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.0016699410609037457 +/- 0.0007672150958651043</t>
+          <t>0.004223968565815361 +/- 0.0010579891566079662</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.0024066797642436355 +/- 0.0017770189111125238</t>
+          <t>0.0021611001964636613 +/- 0.0009624714117026224</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.004764243614931263 +/- 0.0011633319530772847</t>
+          <t>0.0037819253438114097 +/- 0.0012040914216239003</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>4.911591355599709e-05 +/- 0.00014734774066799128</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.004911591355599187 +/- 0.0019768773867876285</t>
+          <t>0.0009823182711198419 +/- 0.001354032293918485</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.002161100196463672 +/- 0.001166438318962469</t>
+          <t>0.0045186640471513 +/- 0.001025570383979416</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>-0.004125736738703323 +/- 0.0009370719070893308</t>
+          <t>-0.0017681728880157177 +/- 0.0013031924520060425</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>-0.0014243614931237158 +/- 0.00026449728915197893</t>
+          <t>-0.001031434184675828 +/- 0.0008633789701005614</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.003094302554027517 +/- 0.0006232110776252158</t>
+          <t>-0.002259332023575633 +/- 0.0006289905930680504</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.0004911591355599599 +/- 0.00038045023047225104</t>
+          <t>0.00014734774066799128 +/- 0.00022507739169726432</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>-0.01542239685658151 +/- 0.0014437071175539373</t>
+          <t>-0.012475442043221985 +/- 0.0011243146505166518</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.0025049115913556184 +/- 0.0008633789701005495</t>
+          <t>-0.0004911591355598932 +/- 0.0006589591289292114</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4.91159135560193e-05 +/- 0.0013441976604522691</t>
+          <t>0.0016208251473477596 +/- 0.0010077742892280366</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.00486247544204319 +/- 0.001086117111370137</t>
+          <t>0.0025540275049115934 +/- 0.0007218535587769773</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-4.911591355595268e-05 +/- 0.0004079874195932187</t>
+          <t>-4.911591355597489e-05 +/- 0.00026449728915197893</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.0004420432220039516 +/- 0.00034381139489194474</t>
+          <t>4.911591355599709e-05 +/- 0.00014734774066799128</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -1046,217 +1046,217 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.003438113948919452 +/- 0.001715545107718375</t>
+          <t>0.0029469548133595367 +/- 0.0009574454169753513</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-4.911591355597489e-05 +/- 0.0009687172359192462</t>
+          <t>0.0015717092337917515 +/- 0.0012770137524557954</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>-4.911591355597489e-05 +/- 0.000264497289151979</t>
+          <t>-0.0002946954813359048 +/- 0.0004501547833944826</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.0004911591355599487 +/- 0.0005380378757418069</t>
+          <t>-0.00019646365422393286 +/- 0.00032579811300149534</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.0006385068762278512 +/- 0.0010545633867182634</t>
+          <t>0.00029469548133597144 +/- 0.0008277160877383277</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.0025540275049116155 +/- 0.0010938633325795937</t>
+          <t>0.004125736738703356 +/- 0.00096247141170261</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.0005402750491159458 +/- 0.0005127851919897027</t>
+          <t>-4.911591355597489e-05 +/- 0.00026449728915197893</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.002946954813359526 +/- 0.0007285067276125467</t>
+          <t>1.1102230246251566e-17 +/- 0.001076075751483624</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.0007367387033399009 +/- 0.0007367387033398713</t>
+          <t>0.002701375245579574 +/- 0.0012665812336176523</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>-0.004960707269155184 +/- 0.0012120788486496084</t>
+          <t>-0.0010314341846758169 +/- 0.000890881981690442</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-0.003929273084479346 +/- 0.0020953564840571186</t>
+          <t>0.001866404715127712 +/- 0.0015960782720306369</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>-0.030844793713163055 +/- 0.0019498460944282162</t>
+          <t>-0.014096267190569722 +/- 0.0010771960805236525</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.00034381139489196854 +/- 0.0009332023575638436</t>
+          <t>-0.003929273084479346 +/- 0.0006946039107922779</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-4.911591355595268e-05 +/- 0.0006752321750917236</t>
+          <t>0.00034381139489196854 +/- 0.0004420432220039208</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.0004911591355599376 +/- 0.0006589591289291948</t>
+          <t>0.0002455795677799966 +/- 0.0006309053329403206</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0.00039292730844796563 +/- 0.0011156990856189036</t>
+          <t>0.0013261296660117884 +/- 0.0006607870357108769</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>-0.006483300589390939 +/- 0.0014201210505698485</t>
+          <t>-0.003290766208251461 +/- 0.0008799839325721348</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-0.015569744597249469 +/- 0.0012239622587796913</t>
+          <t>-0.005697445972495085 +/- 0.0008840864440078873</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-0.015913555992141403 +/- 0.0012070929005348447</t>
+          <t>-0.0009332023575638337 +/- 0.0011081055179448442</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
+          <t>-0.00014734774066794688 +/- 0.0006232110776252165</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>-0.00029469548133591593 +/- 0.0005008860032998832</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>-0.010510805500982334 +/- 0.0007015155627252519</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>-0.006139489194499015 +/- 0.0011879554638946877</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>-0.001080550098231825 +/- 0.00042818260742054153</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>-0.0007367387033398564 +/- 0.0005914339184082748</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>-0.001375245579567752 +/- 0.0010255703839794437</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.0017681728880157288 +/- 0.0009370719070893447</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.0003929273084479545 +/- 0.0005727850584327375</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>-0.0005893909626718763 +/- 0.0009003095667889943</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-0.004862475442043224 +/- 0.00165032393088522</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-0.03344793713163065 +/- 0.0017218613107031575</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>0.0013752455795677855 +/- 0.00048123570585129933</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
           <t>4.911591355599709e-05 +/- 0.00014734774066799128</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>-0.00255402750491156 +/- 0.0008159748391864481</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>-0.010117878192534336 +/- 0.0005469316662897973</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>-0.019253438113948907 +/- 0.0016985870791542668</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-0.012475442043221995 +/- 0.0017599678651442937</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>-0.001375245579567741 +/- 0.0006515962260030477</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>-0.0005402750491159015 +/- 0.0010861171113701335</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>-0.011935166994106083 +/- 0.0006607870357109041</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>9.823182711200529e-05 +/- 0.00029469548133596033</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>-0.0007858546168958535 +/- 0.0013397035065801455</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-0.028683693516699395 +/- 0.0016612509356864137</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-0.04327111984282904 +/- 0.0024699982241021927</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>0.0013261296660117884 +/- 0.0004936088222554344</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.0015225933202357767 +/- 0.0009434858896020936</t>
+          <t>0.0009332023575638782 +/- 0.0013078120781624847</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.0033398821218075026 +/- 0.0006134575636933554</t>
+          <t>0.0034381139489194747 +/- 0.0007285067276125616</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.0011787819253438192 +/- 0.0006662406663187903</t>
+          <t>0.0012278978388998052 +/- 0.0009383582109303742</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.002652259332023621 +/- 0.0006662406663187903</t>
+          <t>0.0004420432220039516 +/- 0.0007750360431266656</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.0017681728880157288 +/- 0.0005008860032998876</t>
+          <t>0.002848722986247554 +/- 0.0008450221283931996</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>0.003880157170923393 +/- 0.0012318208451851072</t>
+          <t>2.2204460492503132e-17 +/- 0.0005380378757418069</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>9.823182711199419e-05 +/- 0.00019646365422398837</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>9.823182711200529e-05 +/- 0.0008731035773394357</t>
+          <t>-0.00024557956777991884 +/- 0.0004528263485900214</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.0007367387033399009 +/- 0.00024557956777992995</t>
+          <t>-4.911591355597489e-05 +/- 0.0005127851919897027</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.00029469548133596033 +/- 0.000500886003299868</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.003438113948919497 +/- 0.0008786121719056227</t>
+          <t>0.0010805500982318695 +/- 0.0004812357058513061</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1281,37 +1281,37 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>-0.00024557956777992995 +/- 0.00024557956777992995</t>
+          <t>0.0005893909626719207 +/- 0.0003675498415298463</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.0011296660117878442 +/- 0.00038360754793254856</t>
+          <t>0.0012278978388998163 +/- 0.000395985154631558</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.0026031434184676126 +/- 0.0009587043858518199</t>
+          <t>-9.823182711197199e-05 +/- 0.0007545329811265962</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.00019646365422398837 +/- 0.0003929273084479351</t>
+          <t>-0.000343811394891913 +/- 0.00031449529653401303</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.0016699410609037567 +/- 0.0008563652148409888</t>
+          <t>0.002996070726915523 +/- 0.000675232175091726</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.003929273084479401 +/- 0.0008507125773913704</t>
+          <t>0.00019646365422399948 +/- 0.0007015155627252285</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.0011296660117878332 +/- 0.0009587043858518336</t>
+          <t>-0.00014734774066796908 +/- 0.0015383555759691321</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.0018315018315018805 +/- 0.0011038735274583407</t>
+          <t>-0.003767660910517989 +/- 0.0015130122757510182</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1331,92 +1331,92 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.000261643118785948 +/- 0.0009138801254093802</t>
+          <t>-0.006436420722134961 +/- 0.0009078676908894415</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.002721088435374175 +/- 0.001014689661416285</t>
+          <t>-5.232862375713632e-05 +/- 0.0007918757692528255</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.0018315018315018694 +/- 0.0008834088443816811</t>
+          <t>0.0012035583464155343 +/- 0.00040869961674027294</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.002302459445316618 +/- 0.0011512297226582888</t>
+          <t>0.005442176870748339 +/- 0.000998366511163714</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.000575614861329099 +/- 0.0012913618711934344</t>
+          <t>0.0010465724751439697 +/- 0.00191554214732842</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-5.232862375719183e-05 +/- 0.00015698587127157548</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.002459445316588138 +/- 0.0007779209182270028</t>
+          <t>0.0013082155939299401 +/- 0.0016589081616062125</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.008058608058608108 +/- 0.002082652929579517</t>
+          <t>0.016326530612244948 +/- 0.0015310035414262523</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.01517530088958663 +/- 0.0010976544721822553</t>
+          <t>0.01972789115646264 +/- 0.002553400920723361</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-0.0034013605442176353 +/- 0.0012656605570327568</t>
+          <t>0.0014652014652015155 +/- 0.0008693483896303669</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.0008372579801151581 +/- 0.0005827068930224982</t>
+          <t>0.0014652014652015044 +/- 0.001041326464789778</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.0008372579801151803 +/- 0.0007098199877682321</t>
+          <t>0.00010465724751443917 +/- 0.0007690705628832544</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.020565149136577743 +/- 0.001887460889259183</t>
+          <t>0.019884877027734227 +/- 0.0031484267831483736</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.028362114076399825 +/- 0.0015310035414262462</t>
+          <t>0.027577184720041913 +/- 0.0014435493693494143</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.0007849293563579774 +/- 0.0011759395632780678</t>
+          <t>0.0008372579801151803 +/- 0.001538141125766524</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.002354788069073832 +/- 0.001078782214970597</t>
+          <t>-0.0017268445839873747 +/- 0.0008123586968215571</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>-0.005337519623233866 +/- 0.001255886970172699</t>
+          <t>-0.0010989010989010395 +/- 0.0021758893653889984</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.00026164311878601465 +/- 0.0013289822186499654</t>
+          <t>0.0018315018315018805 +/- 0.0013082155939299045</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -1426,62 +1426,62 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.0013082155939299178 +/- 0.0008834088443816647</t>
+          <t>0.00026164311878602576 +/- 0.0009138801254093518</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>-0.0029827315541600787 +/- 0.0007040096309300772</t>
+          <t>0.006279434850863463 +/- 0.0015698587127158622</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.0028257456828885918 +/- 0.000627943485086326</t>
+          <t>-0.0026164311878597024 +/- 0.0009360828791207931</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>-0.0002093144950287451 +/- 0.0005827068930225041</t>
+          <t>0.00010465724751442806 +/- 0.0011654137860449983</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.0007326007326007855 +/- 0.0005827068930225201</t>
+          <t>0.002302459445316618 +/- 0.0013685710968730526</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.0001569858712716088 +/- 0.00023979987938024688</t>
+          <t>0.0004709576138147931 +/- 0.0005463268712145899</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>-0.0028780743066456837 +/- 0.001128407046198201</t>
+          <t>0.006541077969649434 +/- 0.0013494292996575241</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.004133961276818443 +/- 0.0015066645786381986</t>
+          <t>0.0028780743066457947 +/- 0.0009433676806551525</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>-0.0019361590790161643 +/- 0.0009078676908894459</t>
+          <t>0.0023024594453166514 +/- 0.001264578333186253</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.0012558869701726483 +/- 0.0009123807312486906</t>
+          <t>-0.002511773940345308 +/- 0.0007690705628832605</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>-0.000261643118785948 +/- 0.00042188685234424006</t>
+          <t>-5.2328623757180724e-05 +/- 0.00028179826306303467</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-5.2328623757169625e-05 +/- 0.0003663003663003777</t>
+          <t>-0.00010465724751437255 +/- 0.0003915915632416401</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1491,122 +1491,122 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.0022501308215593595 +/- 0.0007779209182270155</t>
+          <t>-0.0009942438513866557 +/- 0.0010052000372735906</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.0021454735740450426 +/- 0.0011332500171484896</t>
+          <t>0.01276818419675566 +/- 0.0016247173936431106</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0006279434850864129 +/- 0.00020931449502876732</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-0.0005232862375719183 +/- 0.00033095527578944805</t>
+          <t>-0.0009419152276294529 +/- 0.0005635965261260239</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-0.00015698587127155328 +/- 0.0007779209182270349</t>
+          <t>-0.0010989010989010284 +/- 0.0006802721088435365</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>-0.00010465724751436145 +/- 0.0014196399755364128</t>
+          <t>0.006331763474620666 +/- 0.0017426295976291804</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-0.00026164311878595914 +/- 0.00035103107967027414</t>
+          <t>-0.0003663003663003095 +/- 0.0008453947891890778</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.0006279434850863796 +/- 0.0007326007326007537</t>
+          <t>0.004552590266876033 +/- 0.0009078676908894492</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.002721088435374197 +/- 0.0014948044853046233</t>
+          <t>0.0015175300889587074 +/- 0.0010320817856261683</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>-0.0006279434850863019 +/- 0.00039159156324162234</t>
+          <t>0.0014652014652015266 +/- 0.0009302139630890281</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-0.0034536891679748495 +/- 0.0015021140862802125</t>
+          <t>-0.002773417059131289 +/- 0.0006639758001281873</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>-0.0030350601779172925 +/- 0.0011886778327158903</t>
+          <t>-0.001360544217687032 +/- 0.0012860497883248926</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-0.0069073783359497095 +/- 0.002314321756933132</t>
+          <t>-0.002145473574044943 +/- 0.0012482323853350533</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-0.008267922553636797 +/- 0.0014002185411051407</t>
+          <t>-0.0026164311878597245 +/- 0.0008437737046885007</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0010989010989011394 +/- 0.0006802721088435365</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>-0.0026164311878597024 +/- 0.001146462705400669</t>
+          <t>-0.004604918890633136 +/- 0.0013805239098140095</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>-0.004343275771847144 +/- 0.0013040225844455475</t>
+          <t>0.003192046049188979 +/- 0.0009491552667303629</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.008320251177394055 +/- 0.0026728608663782725</t>
+          <t>0.012297226582940923 +/- 0.001675333395455994</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.0069073783359497876 +/- 0.002706963298038223</t>
+          <t>0.009837781266352753 +/- 0.0024297617511761056</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>0.000523286237571996 +/- 0.0005232862375719626</t>
+          <t>-0.0005232862375719072 +/- 0.0005232862375719405</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>-0.0006802721088434938 +/- 0.00033506667909117936</t>
+          <t>0.00057561486132921 +/- 0.0002817982630630346</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.00020931449502881172 +/- 0.0002563568542944574</t>
+          <t>0.0029304029304029755 +/- 0.0008818576424046413</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>0.005494505494505542 +/- 0.002366388080501299</t>
+          <t>0.003139717425431754 +/- 0.0018574818785241996</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.0001569858712716199 +/- 0.0005756148613291586</t>
+          <t>-0.002616431187859691 +/- 0.00132382110315788</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1616,92 +1616,92 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>0.0008895866038723498 +/- 0.000621367979436827</t>
+          <t>-0.0005756148613291101 +/- 0.0003663003663003427</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-0.0012558869701726593 +/- 0.0009123807312486879</t>
+          <t>-0.0015698587127157993 +/- 0.0018277602508187127</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>0.0010465724751439586 +/- 0.0012602401443005994</t>
+          <t>-0.004029304029303982 +/- 0.0019162567685610092</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.0003139717425432176 +/- 0.0002563568542944574</t>
+          <t>-0.00026164311878595914 +/- 0.00026164311878595914</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-0.005808477237048626 +/- 0.0009198532617083928</t>
+          <t>-0.0007326007326006855 +/- 0.0011271930522520942</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>0.000889586603872361 +/- 0.002132672304794831</t>
+          <t>0.0031920460491889568 +/- 0.0015247307466596883</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-0.00324437467294606 +/- 0.0010413264647897813</t>
+          <t>-0.0007326007326006855 +/- 0.0013685710968730288</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-0.00041862899005752353 +/- 0.0006535843012452632</t>
+          <t>0.0007849293563579662 +/- 0.0007492318714430466</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>-0.00010465724751438366 +/- 0.00031397174254315096</t>
+          <t>0.00010465724751440586 +/- 0.00020931449502881172</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>-0.001412872841444257 +/- 0.0008123586968215521</t>
+          <t>-0.0021978021978021458 +/- 0.0008038875717288012</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.0005756148613291767 +/- 0.0009775793664191438</t>
+          <t>-0.000941915227629464 +/- 0.0009873344983837274</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-0.0019884877027733895 +/- 0.0008372579801151234</t>
+          <t>-0.0021978021978021345 +/- 0.0012558869701726854</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-0.0001569858712715644 +/- 0.0008123586968215607</t>
+          <t>0.0016745159602303051 +/- 0.0008693483896303494</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0.002040816326530659 +/- 0.0011088236577926265</t>
+          <t>-0.002093144950287762 +/- 0.0008756253548237352</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>0.0019361590790162864 +/- 0.0007779209182270237</t>
+          <t>-0.0018838304552589614 +/- 0.0007474022426523116</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>1.1102230246251566e-17 +/- 0.0002340207197802076</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>-0.001726844583987408 +/- 0.0006639758001281803</t>
+          <t>-0.00031397174254313984 +/- 0.0004186289900575568</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>-0.0008372579801150803 +/- 0.00041862899005755405</t>
+          <t>0.0007326007326007745 +/- 0.0005336493473147827</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>-0.00031397174254313984 +/- 0.0007098199877682207</t>
+          <t>-0.0007326007326006855 +/- 0.0005336493473147522</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.00026164311878602576 +/- 0.0005850517994505065</t>
+          <t>-0.0009942438513866447 +/- 0.00043467419481515134</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1726,37 +1726,37 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.00010465724751440586 +/- 0.00020931449502881172</t>
+          <t>-0.0007326007326006855 +/- 0.000479599758760392</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>-5.2328623757169625e-05 +/- 0.0003663003663003777</t>
+          <t>0.0006279434850864019 +/- 0.0003139717425431732</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>-0.00026164311878592585 +/- 0.0008190725192306856</t>
+          <t>-0.0012035583464154453 +/- 0.001194423046626205</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>-0.00026164311878595914 +/- 0.0003510310796702741</t>
+          <t>-5.2328623757169625e-05 +/- 0.0005463268712145751</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>-0.0011512297226582535 +/- 0.0009302139630890067</t>
+          <t>-0.00010465724751435035 +/- 0.0009873344983837122</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>-0.00015698587127153108 +/- 0.0008453947891890854</t>
+          <t>-0.003087388801674451 +/- 0.001108823657792635</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>-0.0006802721088434938 +/- 0.0009078676908894792</t>
+          <t>-0.0004186289900575124 +/- 0.0016179617827043599</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-0.0010593220338982578 +/- 0.000651097772407704</t>
+          <t>0.0013418079096045531 +/- 0.0006662416053712233</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1776,227 +1776,227 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>-0.00014124293785305886 +/- 0.0006156636925904703</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.0020480225988700695 +/- 0.0005866259790196298</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-0.0012711864406779183 +/- 0.00028248587570622874</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-0.00021186440677961604 +/- 0.0005515713047956454</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.0043079096045198105 +/- 0.0008620448881167807</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1.1102230246251566e-17 +/- 0.0003158288103813171</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.0012711864406780183 +/- 0.0007606164981828236</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.003248587570621508 +/- 0.002123346946097862</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.003107344632768394 +/- 0.0026649664214849263</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.001200564971751461 +/- 0.0005515713047956766</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.0015536723163842136 +/- 0.0007606164981828342</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>-0.0014124293785310327 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>-0.004943502824858714 +/- 0.0014473094302202675</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>7.06214689265905e-05 +/- 0.001983696596777988</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>-7.062146892650167e-05 +/- 0.0008620448881167797</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>-0.0005649717514123797 +/- 0.000615663692590478</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.0004237288135593431 +/- 0.00046844982914626625</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>-0.0010593220338982578 +/- 0.0004737432155719881</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>1.1102230246251566e-17 +/- 0.0003158288103813171</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-7.062146892653499e-05 +/- 0.001561676863523726</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.00021186440677969375 +/- 0.0006355932203389827</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.0014830508474576675 +/- 0.0004943502824858575</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>-0.0003531073446327304 +/- 0.0005693684850493128</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>-0.0014124293785310327 +/- 0.0009987383915064099</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0.0004943502824859003 +/- 0.0004521980393667491</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>-0.0019774011299434568 +/- 0.0008820618641805678</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>-0.00014124293785308106 +/- 0.0008235807761080923</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>-0.0016242937853107042 +/- 0.0005515713047956951</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>-0.00028248587570617323 +/- 0.0010569653634954494</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0.0007062146892655718 +/- 0.0004466493870294543</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.0007062146892655718 +/- 0.0004466493870294543</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.0013418079096045531 +/- 0.0008021056985593585</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>-0.001553672316384147 +/- 0.0005284826817477581</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>0.0003531073446327748 +/- 0.0006510977724076921</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>-0.0009887005649716896 +/- 0.00034597312751176554</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
           <t>-0.0009887005649717006 +/- 0.0004684498291462428</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0.00021186440677969375 +/- 0.0006355932203389827</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>-0.0009180790960451546 +/- 0.0005515713047956582</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>-0.0014830508474575788 +/- 0.0005866259790196418</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-0.0009887005649717006 +/- 0.0004684498291462428</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-0.001553672316384147 +/- 0.0009368996582924656</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.001553672316384236 +/- 0.002638635832241467</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-0.0032485875706214306 +/- 0.0017356222778876374</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>-0.001906779661016922 +/- 0.0004521980393667266</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0.0005649717514124797 +/- 0.0015080619000044373</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>-0.0014124293785310437 +/- 0.0006316576207626591</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>-0.005437853107344593 +/- 0.0011409247472742516</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>-0.001553672316384147 +/- 0.0016949152542372937</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>-0.0007062146892654941 +/- 0.0005470315460744781</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>-0.0006355932203389259 +/- 0.00038030824909140163</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>-0.0017655367231638186 +/- 0.00047374321557201287</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>-0.0008474576271186085 +/- 0.0006919462550234902</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>-7.062146892654609e-05 +/- 0.00021186440677963824</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-0.0004943502824858448 +/- 0.0013418079096045369</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>-0.0008474576271185974 +/- 0.0006156636925904907</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0.00035310734463280815 +/- 0.0007236547151101447</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>-0.0009887005649716896 +/- 0.0007202004962701597</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>-0.002048022598870036 +/- 0.00038030824909141605</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>-0.005932203389830448 +/- 0.0012313273851809648</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>-0.0017655367231638075 +/- 0.0005693684850493403</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>-0.002118644067796571 +/- 0.0008356044891383679</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>-0.00021186440677962716 +/- 0.00045219803936670056</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-7.062146892654609e-05 +/- 0.00021186440677963824</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>-0.0012711864406779183 +/- 0.0005284826817477581</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>-0.0012711864406779404 +/- 0.0007606164981828402</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>-7.062146892654609e-05 +/- 0.00021186440677963824</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>-0.002542372881355881 +/- 0.0007864073958799418</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>-0.0024717514124293237 +/- 0.0007236547151101338</t>
-        </is>
-      </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.0009887005649717117 +/- 0.0005649717514124187</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.001906779661016933 +/- 0.00032362822704492004</t>
+          <t>-0.0013418079096044755 +/- 0.0004943502824859003</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.0024717514124293237 +/- 0.0008503950973723334</t>
+          <t>-0.0012005649717513722 +/- 0.000551571304795671</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>-0.0016949152542372614 +/- 0.00046844982914626625</t>
+          <t>-0.0005649717514123909 +/- 0.0006156636925904804</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-0.0047316384180790426 +/- 0.0009501146925899506</t>
+          <t>-0.002330508474576232 +/- 0.0007768361581920806</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>-0.002471751412429346 +/- 0.0007236547151101338</t>
+          <t>-0.0012005649717513611 +/- 0.0003236282270449201</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-0.0006355932203389481 +/- 0.0005866259790196191</t>
+          <t>0.0004943502824859336 +/- 0.0009501146925899566</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -2011,22 +2011,22 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>-0.000706214689265483 +/- 0.00044664938702941923</t>
+          <t>0.001694915254237328 +/- 0.0009043960787334513</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>-0.0048022598870056 +/- 0.0008820618641805625</t>
+          <t>-0.0009887005649717117 +/- 0.0006472564540898061</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-0.003884180790960401 +/- 0.0010593220338982986</t>
+          <t>-0.004025423728813515 +/- 0.0012652876318621966</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-0.00374293785310732 +/- 0.0007097369788927281</t>
+          <t>-0.003319209039547977 +/- 0.001265287631862202</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -2036,172 +2036,172 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>-0.00014124293785309217 +/- 0.00028248587570618434</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>7.062146892655718e-05 +/- 0.00021186440677967158</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-0.0031073446327683275 +/- 0.0007864073958799438</t>
+          <t>-0.0014830508474575788 +/- 0.0010209627326836816</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
+          <t>-0.0013418079096044865 +/- 0.0009180790960451931</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>-0.0003531073446327415 +/- 0.0004737432155719632</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>0.0008474576271186752 +/- 0.0006156636925904983</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>7.062146892657938e-05 +/- 0.0004943502824858654</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>-0.00028248587570618434 +/- 0.00034597312751171117</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.0004237288135593431 +/- 0.00046844982914626625</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>-0.0017655367231637965 +/- 0.000960555826888087</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>0.001694915254237317 +/- 0.0010086763317150719</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>0.0004943502824859003 +/- 0.0003236282270449201</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>-0.0006355932203389369 +/- 0.0008021056985593547</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>-7.062146892652387e-05 +/- 0.0004943502824858575</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>7.062146892655718e-05 +/- 0.00021186440677967158</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>-0.0009887005649717117 +/- 0.0005649717514124187</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>0.0013418079096045755 +/- 0.0004943502824858828</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>0.0009887005649717895 +/- 0.0006472564540898208</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>0.0006355932203390147 +/- 0.00038030824909143866</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>-0.0005649717514123909 +/- 0.0005284826817477106</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>7.062146892655718e-05 +/- 0.00021186440677967158</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>-0.0008474576271185863 +/- 0.0004237288135593209</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>0.0019774011299435123 +/- 0.00028248587570618434</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>0.001129943502824904 +/- 0.0005649717514124381</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>0.0006355932203390147 +/- 0.0003803082490914387</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>0.0005649717514124575 +/- 0.0005284826817477581</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>7.062146892655718e-05 +/- 0.00021186440677967158</t>
+        </is>
+      </c>
+      <c r="CK4" t="inlineStr">
+        <is>
           <t>-0.0013418079096044755 +/- 0.00038030824909143866</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>-7.062146892654609e-05 +/- 0.00021186440677963824</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>-0.0006355932203389259 +/- 0.00038030824909140163</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>-0.002542372881355892 +/- 0.000468449829146216</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>-0.001129943502824815 +/- 0.0006472564540898208</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>-0.00014124293785308106 +/- 0.00042372881355929866</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>-0.002683615819208995 +/- 0.0006919462550234835</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>-0.0014124293785310216 +/- 0.0007062146892655496</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>-0.00035310734463275264 +/- 0.0005693684850493128</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>-0.0009887005649717006 +/- 0.0004684498291462428</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>-0.001977401129943479 +/- 0.00042372881355932094</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>-0.0005649717514123797 +/- 0.00042372881355929866</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>-0.0021892655367231283 +/- 0.0004943502824858575</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>-0.0010593220338982468 +/- 0.0005693684850493609</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>-0.0021892655367231283 +/- 0.0006662416053712187</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>-0.0006355932203389259 +/- 0.00038030824909140163</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>-0.0006355932203389481 +/- 0.0005866259790196191</t>
-        </is>
-      </c>
-      <c r="CH4" t="inlineStr">
-        <is>
-          <t>-0.0006355932203389147 +/- 0.00021186440677963824</t>
-        </is>
-      </c>
-      <c r="CI4" t="inlineStr">
-        <is>
-          <t>-0.0007768361581920513 +/- 0.0005866259790196232</t>
-        </is>
-      </c>
-      <c r="CJ4" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CK4" t="inlineStr">
-        <is>
-          <t>-0.0010593220338982689 +/- 0.000651097772407686</t>
         </is>
       </c>
     </row>
@@ -2211,167 +2211,167 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>0.0011273957158963177 +/- 0.0013575642140690228</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>-0.00039458850056368623 +/- 0.0009449297978714798</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.0023111612175873986 +/- 0.0006880809253513997</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-0.001465614430665163 +/- 0.0006277073689774529</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-0.000394588500563664 +/- 0.00123628591879716</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-0.0008455467869221911 +/- 0.0008455467869222207</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-0.00016910935738442267 +/- 0.0005665093360271094</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-0.001014656144306636 +/- 0.0016683933017980512</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-0.019616685456595218 +/- 0.002180279549697158</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-0.010484780157835372 +/- 0.0012903633756775276</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>-0.0012965050732807182 +/- 0.0010099477377209119</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.0014092446448703776 +/- 0.0009176336299943408</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>-0.0009582863585118062 +/- 0.00036094274168170125</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>-0.003664036076662902 +/- 0.001134420056228755</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>-0.005298759864712499 +/- 0.0005166376206263866</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>-0.001578354002254778 +/- 0.001149722550979207</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>-0.0005073280721533014 +/- 0.0007749564309395637</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>-0.0012401352874858995 +/- 0.0007891770011273978</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0.0008455467869222244 +/- 0.0006787821070345022</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>-5.636978579480756e-05 +/- 0.00016910935738442264</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-0.0012401352874858774 +/- 0.0008659690809322091</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>-0.0028184892897406776 +/- 0.0004366384832251812</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>-0.003043968432919919 +/- 0.0017501888045388942</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3.3306690738754695e-17 +/- 0.00043663848322518116</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0.000789177001127428 +/- 0.0007218854833633348</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>0.00022547914317926353 +/- 0.0003739148579882117</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0.00033821871476891197 +/- 0.0002761544242145864</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0.00033821871476890085 +/- 0.000373914857988215</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.00033821871476891197 +/- 0.0002761544242145864</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-0.0002818489289740489 +/- 0.0003781400187429</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.0015783540022548225 +/- 0.0009364852156615899</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-0.006877113866967266 +/- 0.0010930507006575762</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-0.007497181510710227 +/- 0.0010710259301014535</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>-0.0003945885005636529 +/- 0.0002583188103131521</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0.0006764374295377795 +/- 0.0004218328508200486</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0.0005636978579481533 +/- 0.00043663848322518116</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-0.000676437429537724 +/- 0.0007040583989175228</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>-0.003494926719278424 +/- 0.0008659690809322062</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>-0.00033821871476885645 +/- 0.0015375627617797206</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>-0.016178128523111613 +/- 0.0007152523979960314</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>-0.0021420518602029205 +/- 0.0008284632726436958</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>-0.004002254791431759 +/- 0.0007328072153325769</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>0.0007891770011274057 +/- 0.00037391485798818824</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0.00022547914317927464 +/- 0.00027615442421458644</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>0.0004509582863585382 +/- 0.0004914203994972448</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>-0.0010146561443066249 +/- 0.0004218328508200516</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>-0.0005636978579480978 +/- 0.0003565138286548287</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>-0.0006764374295377129 +/- 0.00022547914317927464</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>-0.0010710259301014325 +/- 0.0007749564309395354</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>-0.01335963923337088 +/- 0.0009106817599438222</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>3.3306690738754695e-17 +/- 0.00043663848322518116</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0.0002818489289741044 +/- 0.00037814001874292476</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.0008455467869221689 +/- 0.000630233364571543</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.0004509582863585382 +/- 0.0004914203994972449</t>
+          <t>-0.004171364148816204 +/- 0.000676437429537774</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.015614430665163414 +/- 0.0009106817599438241</t>
+          <t>-0.015839909808342722 +/- 0.0009245332281204686</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2396,257 +2396,257 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.00022547914317927464 +/- 0.00027615442421458644</t>
+          <t>0.00016910935738445598 +/- 0.00025831881031320293</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-0.0005636978579480978 +/- 0.0003565138286548287</t>
+          <t>-0.00028184892897406 +/- 0.0008823267104001341</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>-0.00033821871476884534 +/- 0.000276154424214532</t>
+          <t>-0.005355129650507296 +/- 0.0009844559862780733</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-0.0005636978579480756 +/- 0.0</t>
+          <t>0.0015783540022548225 +/- 0.0005523088484291524</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.0002818489289740378 +/- 0.0002818489289740378</t>
+          <t>-0.0015219842164599594 +/- 0.0009779792318431481</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2.2204460492503132e-17 +/- 0.0005041866916572041</t>
+          <t>-0.001409244644870322 +/- 0.0010162207653506368</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.0015783540022548225 +/- 0.0007891770011274073</t>
+          <t>0.0012965050732807516 +/- 0.0010099477377209247</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-0.0024239007891769804 +/- 0.0012103106287251525</t>
+          <t>-0.009864712514092423 +/- 0.0010470223010714075</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.00033821871476891197 +/- 0.00027615442421458644</t>
+          <t>0.00016910935738445598 +/- 0.00044026210123486735</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
+          <t>-0.0014092446448703334 +/- 0.0008455467869222207</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>-0.0037204058624576986 +/- 0.00129036337567752</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>-0.00011273957158961512 +/- 0.00022547914317923027</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>-0.0007328072153325649 +/- 0.000758377905697526</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>-0.006031567080045086 +/- 0.0007152523979960182</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-0.006595264937993217 +/- 0.0018873358560071258</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-0.00839909808342727 +/- 0.0012207670703330083</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>0.00016910935738445598 +/- 0.00025831881031320293</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.0005073280721533457 +/- 0.0007328072153325811</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>-5.636978579480756e-05 +/- 0.00016910935738442264</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>-0.004284103720405841 +/- 0.001133018672054201</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>-0.006877113866967277 +/- 0.0010635829912126879</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>-0.00033821871476883423 +/- 0.00037391485798819165</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>2.2204460492503132e-17 +/- 0.0007130276573096661</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>-0.00924464487034946 +/- 0.0006277073689774748</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>0.001183765501691103 +/- 0.000531791495606354</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>-0.0007891770011273725 +/- 0.0006764374295377888</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>-0.007158962795941348 +/- 0.001236285918797145</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>-0.0035512965050732647 +/- 0.0011837655016910989</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>0.0002818489289741044 +/- 0.0005197037461833535</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>0.0007328072153326204 +/- 0.00036094274168165967</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>-0.002311161217587365 +/- 0.0006402376940022588</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>-0.0005636978579481311 +/- 0.0009432469295761765</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>-0.000394588500563664 +/- 0.00036094274168165267</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>-0.0006764374295377462 +/- 0.0004914203994972525</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>0.0012401352874859216 +/- 0.0006573790185846012</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>-0.0003945885005636751 +/- 0.00044026210123486025</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>-0.00011273957158961512 +/- 0.0004218328508200575</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>1.1102230246251566e-17 +/- 0.00025209334582860826</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>0.00033821871476890085 +/- 0.0005166376206263526</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>5.636978579482976e-05 +/- 0.0005885178415394845</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>-0.00011273957158959291 +/- 0.0004218328508200486</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>-0.0013528748590755147 +/- 0.0005748612754896165</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>-0.0009582863585118062 +/- 0.00044026210123490996</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>0.00011273957158963732 +/- 0.00022547914317927464</t>
         </is>
       </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>0.00011273957158963732 +/- 0.0004218328508200516</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>3.3306690738754695e-17 +/- 0.0006669763002366995</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>-0.00033821871476884534 +/- 0.00045095828635850207</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>-0.0012401352874858774 +/- 0.0013528748590755433</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-0.001747463359639201 +/- 0.0008149285397294977</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>-0.006313416009019146 +/- 0.001002051230813477</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-0.0006764374295377351 +/- 0.000747829715976415</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>5.636978579481866e-05 +/- 0.00016910935738445598</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>-0.0036076662908680612 +/- 0.0008436657016401105</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0.0005073280721533457 +/- 0.0003945885005636957</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>-0.002142051860202909 +/- 0.0014656144306651672</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>-0.00011273957158960401 +/- 0.000491420399497255</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>-0.000394588500563664 +/- 0.00036094274168165267</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>5.636978579484087e-05 +/- 0.0003945885005636957</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>5.636978579481866e-05 +/- 0.00016910935738445598</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>-0.00033821871476885645 +/- 0.00037391485798818824</t>
-        </is>
-      </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>0.00011273957158963732 +/- 0.00022547914317927464</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CH5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.0014092446448703334 +/- 0.0009516315116197566</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.00011273957158963732 +/- 0.00022547914317927464</t>
+          <t>-0.0007891770011273725 +/- 0.0009159006093163587</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.00033821871476891197 +/- 0.0005748612754895862</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.005595567867036045 +/- 0.0009086548181084231</t>
+          <t>0.0004986149584487287 +/- 0.00046020076802867936</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2666,157 +2666,157 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.00022160664819942388 +/- 0.0008291761521936553</t>
+          <t>-0.0018282548476454496 +/- 0.000702968284789456</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.0028808864265928214 +/- 0.001183055761997938</t>
+          <t>-0.0013296398891966877 +/- 0.0009659609847181527</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.000221606648199435 +/- 0.0008291761521936671</t>
+          <t>0.00027700831024929373 +/- 0.00027700831024929373</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.00166204986149584 +/- 0.00042913942894267173</t>
+          <t>0.0010526315789473606 +/- 0.0005226582344629955</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.003047091412742409 +/- 0.0010584472672876836</t>
+          <t>-0.001274238227146851 +/- 0.0003547437250655367</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0003878116343490112 +/- 0.0004986149584487287</t>
+          <t>5.540166204985875e-05 +/- 0.00016620498614957623</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.0021052631578947433 +/- 0.0009531662345753581</t>
+          <t>-0.0027146814404432453 +/- 0.0006762634690157341</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-0.021385041551246552 +/- 0.0019852047498248077</t>
+          <t>-0.003933518005540204 +/- 0.0009086548181084142</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.022991689750692535 +/- 0.0016104644713294772</t>
+          <t>-0.00459833795013852 +/- 0.0006094182825484805</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.00022160664819942388 +/- 0.001140790043322675</t>
+          <t>-0.0015512465373961448 +/- 0.0005428232116970966</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>-0.004155124653739639 +/- 0.0009675484319431074</t>
+          <t>-0.0007202216066482081 +/- 0.0004986149584487756</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-0.011246537396121904 +/- 0.0016444124187984395</t>
+          <t>0.0019390581717451227 +/- 0.0007932310838380323</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.0020498614958448626 +/- 0.0009926023749124145</t>
+          <t>-0.0006648199445983494 +/- 0.0018341213692240207</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.012132963988919655 +/- 0.002194493331893448</t>
+          <t>0.012465373961218829 +/- 0.002517577344598725</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0.0013850415512465242 +/- 0.0007116472342750886</t>
+          <t>0.0008310249307478923 +/- 0.00044666247913011206</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-0.005872576177285349 +/- 0.0009001704603474821</t>
+          <t>0.0004986149584487287 +/- 0.0005784103329036029</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.0019944598337950257 +/- 0.001218836565096958</t>
+          <t>0.0017174515235456988 +/- 0.00046020076802872343</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.012188365650969545 +/- 0.001886912616723138</t>
+          <t>0.0006094182825484463 +/- 0.0003878116343490112</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-0.0001108033240997175 +/- 0.0003324099722991525</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.000941828254847632 +/- 0.001136747065300994</t>
+          <t>0.0009972299168974797 +/- 0.00041458807609685063</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.001772853185595591 +/- 0.0013525269380314318</t>
+          <t>0.0004986149584487287 +/- 0.00046020076802867936</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.0005540166204985875 +/- 0.00035039087647293325</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-0.0009972299168975352 +/- 0.00033240997229919687</t>
+          <t>-0.00016620498614958735 +/- 0.00035474372506554366</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.00035039087647293325</t>
+          <t>-0.00016620498614957623 +/- 0.00035474372506551417</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.00044321329639888105 +/- 0.00041458807609683285</t>
+          <t>0.0 +/- 0.00024776376481990903</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0.002659279778393353 +/- 0.0007349861031258508</t>
+          <t>0.0012188365650969367 +/- 0.0004145880760968625</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-0.00038781163434905566 +/- 0.0012150533074493865</t>
+          <t>-0.0004432132963989033 +/- 0.000542823211697117</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-0.002714681440443234 +/- 0.001274238227146816</t>
+          <t>0.00033240997229915247 +/- 0.00044321329639886994</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-0.001772853185595591 +/- 0.0012087215639485617</t>
+          <t>-5.540166204985875e-05 +/- 0.0003878116343490112</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>5.540166204985875e-05 +/- 0.0002983470807276585</t>
+          <t>0.000221606648199435 +/- 0.0003674930515629069</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.0006094182825484463 +/- 0.00046020076802867936</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -2826,97 +2826,97 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.003434903047091431 +/- 0.0012584838439446582</t>
+          <t>0.0009972299168974907 +/- 0.0004829804923590993</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.0015512465373961116 +/- 0.0007756232686980716</t>
+          <t>0.0006648199445983049 +/- 0.00048298049235905347</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>-0.00027700831024929373 +/- 0.00027700831024929373</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>5.540166204984764e-05 +/- 0.0005226582344629685</t>
+          <t>0.0001108033240997175 +/- 0.000221606648199435</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.0005540166204985985 +/- 0.000606894800559731</t>
+          <t>0.00027700831024929373 +/- 0.00027700831024929373</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>-0.0018836565096952973 +/- 0.0011407900433226586</t>
+          <t>0.0004986149584487398 +/- 0.0006292419219723188</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>0.0005540166204985875 +/- 0.0004291394289426288</t>
+          <t>0.00016620498614957623 +/- 0.00025388230996984003</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.000221606648199435 +/- 0.00044321329639886994</t>
+          <t>-0.0001108033240997175 +/- 0.000221606648199435</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.001052631578947394 +/- 0.00155618525265243</t>
+          <t>-0.0001108033240997175 +/- 0.00048298049235905347</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.0012742382271468066 +/- 0.0009611829126258991</t>
+          <t>0.0003878116343490112 +/- 0.0004327008130695992</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.000221606648199435 +/- 0.0012188365650969732</t>
+          <t>-0.0014404432132964274 +/- 0.0008291761521936568</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>-0.0035457063711911373 +/- 0.0009972299168975044</t>
+          <t>0.0015512465373961337 +/- 0.0002216066481994794</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.0004986149584487398 +/- 0.0005226582344629685</t>
+          <t>-0.0003878116343490112 +/- 0.00025388230996984003</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-2.2204460492503132e-17 +/- 0.0007432912944597602</t>
+          <t>0.001108033240997197 +/- 0.0003503908764729683</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.0004986149584487287 +/- 0.00016620498614957626</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>-0.0048199445983379665 +/- 0.0008600650801252086</t>
+          <t>-0.0006094182825484684 +/- 0.00029834708072769565</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>-0.020000000000000028 +/- 0.001926353313098478</t>
+          <t>-0.002437673130193896 +/- 0.00044321329639887</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-0.0017728531855955797 +/- 0.0009204015360574069</t>
+          <t>-0.0032132963988919737 +/- 0.0009204015360574055</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-0.007645429362880918 +/- 0.002412359119897744</t>
+          <t>-0.002437673130193929 +/- 0.0006169267992055599</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -2926,22 +2926,22 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>5.540166204985875e-05 +/- 0.00016620498614957623</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>-0.00016620498614957623 +/- 0.00025388230996984003</t>
+          <t>-5.540166204985875e-05 +/- 0.00016620498614957623</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-0.013795013850415516 +/- 0.0019422214008817803</t>
+          <t>-0.0017174515235457322 +/- 0.000874223481332935</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-0.0026038781163435164 +/- 0.0007453531328018735</t>
+          <t>-0.004487534626038792 +/- 0.0006292419219723169</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2951,42 +2951,42 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
+          <t>0.000221606648199435 +/- 0.0002714116058485381</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>-0.0004986149584487398 +/- 0.00029834708072768123</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>0.0007756232686980224 +/- 0.000367493051562907</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
           <t>0.00044321329639887 +/- 0.00022160664819943497</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>-0.001052631578947394 +/- 0.00038781163434905403</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>-0.0049861495844875535 +/- 0.0021599544254424304</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>-0.0006094182825484906 +/- 0.0007202216066482115</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>-0.0030470914127423976 +/- 0.0011686993412592366</t>
-        </is>
-      </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-0.0007756232686980669 +/- 0.0005649883117554532</t>
+          <t>-0.0017174515235457322 +/- 0.0003878116343490112</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-0.0014404432132964161 +/- 0.0013388416591240465</t>
+          <t>0.0008310249307478923 +/- 0.0006194094120497874</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-0.008254847645429353 +/- 0.0011739401717682728</t>
+          <t>-0.0004986149584487398 +/- 0.00029834708072768123</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2996,47 +2996,47 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>-0.005706371191135739 +/- 0.0008600650801252107</t>
+          <t>-0.0011080332409972415 +/- 0.00065552130560662</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>-0.0059833795013850555 +/- 0.0010742780847460083</t>
+          <t>0.00033240997229915247 +/- 0.0003674930515629069</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-5.540166204985875e-05 +/- 0.0004602007680286794</t>
+          <t>0.0003878116343490112 +/- 0.00025388230996984003</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>-0.006149584487534654 +/- 0.0008383792770316676</t>
+          <t>-0.0011080332409972304 +/- 0.0007834978184892575</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>-0.007922437673130223 +/- 0.0006094182825484825</t>
+          <t>-0.001772853185595591 +/- 0.00048298049235905347</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>-0.012465373961218862 +/- 0.0018909748660250662</t>
+          <t>0.0007202216066481637 +/- 0.00025388230996984003</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>0.00016620498614957623 +/- 0.00025388230996984</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>0.0003878116343490112 +/- 0.0004327008130695992</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>-0.00027700831024930485 +/- 0.0003716456472298884</t>
+          <t>0.0003878116343490112 +/- 0.00035474372506551417</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3046,12 +3046,12 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-5.540166204985875e-05 +/- 0.0002983470807276585</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>-0.001052631578947394 +/- 0.0009418282548476425</t>
+          <t>0.0006094182825484463 +/- 0.0002983470807276585</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3061,37 +3061,37 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.00044321329639887 +/- 0.00022160664819943497</t>
+          <t>0.000221606648199435 +/- 0.0002714116058485381</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>0.0008864265927977621 +/- 0.000507764619939714</t>
+          <t>0.00044321329639887 +/- 0.00048298049235905347</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>-0.011024930747922457 +/- 0.0016331748446519253</t>
+          <t>0.0001108033240997175 +/- 0.000221606648199435</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>0.0007756232686980224 +/- 0.000367493051562907</t>
+          <t>0.0001108033240997175 +/- 0.00041458807609681507</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>-0.0013296398891967098 +/- 0.0008654016261392511</t>
+          <t>0.0006648199445983161 +/- 0.00041458807609684174</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>-0.012963988919667602 +/- 0.0017554547942110667</t>
+          <t>0.000221606648199435 +/- 0.0003674930515629069</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>0.00016620498614958735 +/- 0.0006578582873705143</t>
+          <t>-0.000221606648199435 +/- 0.000367493051562907</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-0.003515151515151538 +/- 0.002042702975315494</t>
+          <t>-0.0033939393939394157 +/- 0.0017397212235645352</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3111,157 +3111,157 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.01042424242424247 +/- 0.002390676717977679</t>
+          <t>-0.017454545454545455 +/- 0.0010427060929748707</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0041818181818181425 +/- 0.002461083697484444</t>
+          <t>0.0007878787878787708 +/- 0.0018591347454761024</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.00248484848484849 +/- 0.0011953383589888354</t>
+          <t>-0.001030303030303048 +/- 0.0022684808814803434</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.018545454545454552 +/- 0.0017184784095464142</t>
+          <t>0.003333333333333288 +/- 0.001562884479785134</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.037515151515151536 +/- 0.003700941731096272</t>
+          <t>-0.018060606060606076 +/- 0.00240599190803384</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.00060606060606061 +/- 0.00060606060606061</t>
+          <t>0.000363636363636366 +/- 0.0005554637206007114</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.008363636363636306 +/- 0.002006417619060237</t>
+          <t>0.021757575757575708 +/- 0.0029498408542152385</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.012060606060606027 +/- 0.0031075015135259036</t>
+          <t>0.01654545454545452 +/- 0.0024848484848484674</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.01157575757575754 +/- 0.0031776307221620397</t>
+          <t>0.014969696969696944 +/- 0.0034609191600652733</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.007757575757575697 +/- 0.002215232349393598</t>
+          <t>0.0013939393939394029 +/- 0.0010159427038933528</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-0.004484848484848513 +/- 0.002238325492438728</t>
+          <t>-0.011090909090909162 +/- 0.0014857758390462233</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-0.0037575757575757816 +/- 0.001479582498876822</t>
+          <t>-0.0005454545454545601 +/- 0.0022910373541134184</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-0.004121212121212159 +/- 0.005792874252290176</t>
+          <t>-0.0043030303030303415 +/- 0.0037988930773854117</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.017939393939393932 +/- 0.001842264745887345</t>
+          <t>0.013878787878787857 +/- 0.0020721601208822872</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.011454545454545417 +/- 0.002648006336358014</t>
+          <t>0.016787878787878786 +/- 0.0017988875248067789</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.0013939393939394029 +/- 0.0013833590558198063</t>
+          <t>0.0016969696969696857 +/- 0.0011109274412013962</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.007696969696969635 +/- 0.0021177460860189404</t>
+          <t>0.00042424242424242696 +/- 0.0011191627462193642</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0.0009696969696969427 +/- 0.00274003746798963</t>
+          <t>-0.00121212121212122 +/- 0.0021168786904937086</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.000242424242424244 +/- 0.0004020151261036874</t>
+          <t>0.00121212121212122 +/- 0.00046945252681302325</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.015999999999999993 +/- 0.0014894794821144952</t>
+          <t>0.007757575757575697 +/- 0.001322268135107368</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>-0.005393939393939428 +/- 0.0026201171298445365</t>
+          <t>0.003454545454545388 +/- 0.0013565472294302383</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.003090909090909055 +/- 0.0011642044068059308</t>
+          <t>0.0019393939393939185 +/- 0.0010773568990685232</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.0023030303030302846 +/- 0.0018738939192412196</t>
+          <t>0.0046666666666665855 +/- 0.0007690046994211881</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.004424242424242364 +/- 0.00210033011529252</t>
+          <t>0.0069696969696969036 +/- 0.0015628844797851767</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.000242424242424244 +/- 0.0006748805288278858</t>
+          <t>0.0005454545454545489 +/- 0.0005034317492677654</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0.000242424242424244 +/- 0.002120346143580123</t>
+          <t>0.00672727272727266 +/- 0.0013939393939394029</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-0.021454545454545483 +/- 0.002883727818998884</t>
+          <t>0.0027272727272726893 +/- 0.0020686118988940284</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>-0.008424242424242478 +/- 0.0015908369392008208</t>
+          <t>0.0007878787878787818 +/- 0.0016497766774322582</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-0.00484848484848488 +/- 0.001626231256363494</t>
+          <t>-0.001515151515151536 +/- 0.002032789070454339</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-0.005151515151515185 +/- 0.0012196734422726205</t>
+          <t>6.0606060606061e-05 +/- 0.0005034317492677654</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.0007878787878787929 +/- 0.0009009738634738546</t>
+          <t>-0.000484848484848488 +/- 0.0004535342286998746</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -3271,122 +3271,122 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.013878787878787924 +/- 0.001905961841638315</t>
+          <t>0.0018787878787878687 +/- 0.001030303030303012</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.012666666666666692 +/- 0.002648006336357965</t>
+          <t>-0.0037575757575757816 +/- 0.0013497610576557715</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>0.000303030303030305 +/- 0.0004886216817150667</t>
+          <t>-0.000121212121212122 +/- 0.000652747249349641</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-0.0018787878787878908 +/- 0.0013125095653156278</t>
+          <t>-0.0046666666666666965 +/- 0.0016718926332283408</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-0.004303030303030331 +/- 0.0023852931702005517</t>
+          <t>0.004424242424242353 +/- 0.0012136354178485164</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>-0.013575757575757607 +/- 0.0014393141923682044</t>
+          <t>-0.001454545454545464 +/- 0.001021351487657747</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-0.0015757575757575858 +/- 0.001333333333333342</t>
+          <t>-0.001030303030303037 +/- 0.0009791208740244617</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.009939393939393892 +/- 0.001901137835316148</t>
+          <t>0.0023636363636363343 +/- 0.000876171654230333</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.0016969696969697079 +/- 0.002666666666666684</t>
+          <t>-0.00545454545454549 +/- 0.0021851825911903106</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.0012727272727272477 +/- 0.0027964295745598173</t>
+          <t>0.0021212121212121236 +/- 0.0011257076133943265</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-0.011636363636363677 +/- 0.0038787878787878653</t>
+          <t>-0.007515151515151563 +/- 0.0028964371261451147</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.0065454545454544984 +/- 0.002652856803422927</t>
+          <t>0.0012121212121211755 +/- 0.0020100756305183867</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-0.0034545454545454766 +/- 0.0007690046994211881</t>
+          <t>-0.0012727272727272808 +/- 0.001132214648016335</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>0.000969696969696976 +/- 0.0009847319278346682</t>
+          <t>0.0024242424242423843 +/- 0.001355192713636205</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-0.003575757575757599 +/- 0.001030303030303037</t>
+          <t>-0.0015757575757575858 +/- 0.0004020151261036874</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>-0.008787878787878844 +/- 0.002472994637951915</t>
+          <t>-0.000181818181818183 +/- 0.0010858468404344869</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.006060606060606 +/- 0.0017978662999019678</t>
+          <t>0.0018181818181817965 +/- 0.001212121212121181</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-0.006909090909090953 +/- 0.0018019477269477094</t>
+          <t>-0.00018181818181819409 +/- 0.0023323492611992493</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-0.01509090909090911 +/- 0.0033355364620162274</t>
+          <t>-0.006909090909090953 +/- 0.0023347103374858603</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>0.0015757575757575748 +/- 0.001021351487657718</t>
+          <t>-6.0606060606061e-05 +/- 0.00018181818181818297</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>-0.0075757575757576245 +/- 0.0017617505277271184</t>
+          <t>-0.0007878787878787929 +/- 0.0009009738634738546</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.005454545454545401 +/- 0.0012712834523274223</t>
+          <t>0.007090909090909025 +/- 0.0011829831088450461</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0.0016969696969696634 +/- 0.0036242221546002344</t>
+          <t>0.003575757575757532 +/- 0.00241589471854479</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-0.003939393939393965 +/- 0.002335496832484584</t>
+          <t>-0.005030303030303063 +/- 0.0013012673062778198</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3396,77 +3396,77 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>0.0010909090909090979 +/- 0.0005938156952201683</t>
+          <t>-0.0008484848484848539 +/- 0.0006180629713445839</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-0.00242424242424244 +/- 0.001626231256363494</t>
+          <t>-0.0022424242424242567 +/- 0.0012727272727272808</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>0.015151515151515138 +/- 0.0021513017393089647</t>
+          <t>0.0044848484848484475 +/- 0.003232070697205646</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.000484848484848488 +/- 0.001077356899068563</t>
+          <t>-0.0024848484848485008 +/- 0.0006327458490248859</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.004969696969696913 +/- 0.0016442012080303482</t>
+          <t>-0.0012727272727272808 +/- 0.0013673350512337637</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-0.001212121212121231 +/- 0.002777318603003538</t>
+          <t>-0.008606060606060662 +/- 0.0010773568990685633</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>0.012121212121212088 +/- 0.002737355100760312</t>
+          <t>0.004121212121212059 +/- 0.002215232349393563</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-0.006121212121212161 +/- 0.0017449915210773408</t>
+          <t>-0.002606060606060623 +/- 0.000815371154368109</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>0.000484848484848488 +/- 0.0005938156952201681</t>
+          <t>-0.000181818181818183 +/- 0.00027773186030035567</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>-0.000303030303030305 +/- 0.0018232253280595662</t>
+          <t>0.0015757575757575748 +/- 0.0012181667419540363</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.0015151515151515138 +/- 0.0010231480615838706</t>
+          <t>-0.001636363636363647 +/- 0.0015815743455393906</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.0037575757575757152 +/- 0.0010427060929748266</t>
+          <t>0.0015151515151515138 +/- 0.0008243315459839512</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-0.003272727272727294 +/- 0.0012770489397397342</t>
+          <t>0.0022424242424242125 +/- 0.001604630581196783</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>0.0016969696969696857 +/- 0.002495910337208958</t>
+          <t>-0.001030303030303037 +/- 0.0016273601917694107</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>-0.011818181818181872 +/- 0.0014658650451451637</t>
+          <t>-0.0008484848484848539 +/- 0.0007761362712039866</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>-0.0012727272727272808 +/- 0.000688352526763674</t>
+          <t>0.000121212121212122 +/- 0.0004535342286998746</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>0.002060606060606074 +/- 0.0008221006040151893</t>
+          <t>0.00042424242424242696 +/- 0.00047334846520646694</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>0.0016969696969696968 +/- 0.0011109274412014036</t>
+          <t>6.0606060606061e-05 +/- 0.00018181818181818297</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>-0.019393939393939418 +/- 0.002528079226013833</t>
+          <t>-0.002909090909090928 +/- 0.0008907235428302523</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3506,37 +3506,37 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>0.000363636363636366 +/- 0.0006180629713445839</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>-0.0060606060606061 +/- 0.0017354934622153266</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>-0.003878787878787904 +/- 0.0014894794821144954</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>6.0606060606061e-05 +/- 0.00018181818181818297</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>0.0008484848484848429 +/- 0.0016531129329679743</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>-0.01357575757575762 +/- 0.0020137269970710134</t>
-        </is>
-      </c>
-      <c r="CH7" t="inlineStr">
-        <is>
-          <t>6.0606060606061e-05 +/- 0.00018181818181818297</t>
-        </is>
-      </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>0.000303030303030305 +/- 0.0014405896150308838</t>
+          <t>0.0007878787878787929 +/- 0.0015102952478032962</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>-0.002606060606060623 +/- 0.002100330115292554</t>
+          <t>-0.005515151515151551 +/- 0.0015675778371366843</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>-0.0111515151515152 +/- 0.002102951705805732</t>
+          <t>-0.000666666666666671 +/- 0.0013402026901512803</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.010806451612903157 +/- 0.0013267701805648453</t>
+          <t>-0.001129032258064544 +/- 0.0009139784946236507</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3556,157 +3556,157 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.006989247311827917 +/- 0.0005376344086021612</t>
+          <t>-0.0010752688172043444 +/- 0.0009617496677418578</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.005537634408602099 +/- 0.0010766120642204651</t>
+          <t>-0.0020430107526882234 +/- 0.0005790499792617676</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.0012365591397849097 +/- 0.0007992510079203517</t>
+          <t>-0.0009139784946237128 +/- 0.0007233131208104169</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.004193548387096735 +/- 0.0006715051611181099</t>
+          <t>0.0056989247311827525 +/- 0.001321312443811238</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.0017204301075268269 +/- 0.0004023287512660172</t>
+          <t>-0.0011290322580645774 +/- 0.00044659268080205785</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.00010752688172044333 +/- 0.00021505376344088667</t>
+          <t>5.376344086021057e-05 +/- 0.0001612903225806317</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.006021505376344038 +/- 0.001148072930325965</t>
+          <t>0.0009139784946236129 +/- 0.000540315893608648</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.006612903225806521 +/- 0.0009928056619687808</t>
+          <t>0.003387096774193499 +/- 0.0012734106755190146</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.005591397849462443 +/- 0.0016518593006168987</t>
+          <t>0.007795698924731131 +/- 0.0017545342873205175</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.0008602150537634801 +/- 0.0008046575025320448</t>
+          <t>0.0059139784946236175 +/- 0.0007974406975371539</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-0.000483870967741884 +/- 0.0010327619737794916</t>
+          <t>0.002795698924731127 +/- 0.0010698789646307841</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-0.005268817204301013 +/- 0.0010698789646307674</t>
+          <t>-0.0011290322580645774 +/- 0.0010327619737794899</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.004408602150537688 +/- 0.001014406573339414</t>
+          <t>0.011182795698924686 +/- 0.0015729826707879325</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-0.004408602150537589 +/- 0.0014183769847605123</t>
+          <t>-0.002419354838709731 +/- 0.0007697753259825781</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>-0.003602150537634341 +/- 0.0009928056619687754</t>
+          <t>0.0001612903225806095 +/- 0.0005403158936086336</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-0.0024193548387096307 +/- 0.0008064516129032252</t>
+          <t>0.0007526881720429701 +/- 0.0007292827938844354</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>-0.0008602150537634024 +/- 0.0011328659949303929</t>
+          <t>-0.0004301075268817511 +/- 0.0005267719876953333</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>-0.008494623655913924 +/- 0.0010425117972938205</t>
+          <t>-0.0003763440860215628 +/- 0.0006384054885504134</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.0008064516129032695 +/- 0.0002688172043010528</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.002526881720430163 +/- 0.0009928056619687988</t>
+          <t>0.00010752688172039892 +/- 0.00046869881113339724</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.00010752688172046553 +/- 0.0007901579815429641</t>
+          <t>0.0018279569892472591 +/- 0.0009060376100189892</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>-0.0016666666666666275 +/- 0.0008817859928417745</t>
+          <t>0.0015591397849461952 +/- 0.0008135884919581742</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>-0.000483870967741884 +/- 0.0006989247311827877</t>
+          <t>-0.0009139784946237018 +/- 0.00034425399125982437</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.0020967741935483232 +/- 0.0008483727869924598</t>
+          <t>-0.0008602150537634689 +/- 0.0003566263215435884</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.0001612903225806317 +/- 0.00024637503736319664</t>
+          <t>-5.376344086022167e-05 +/- 0.000161290322580665</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>-0.002096774193548334 +/- 0.001369649376651298</t>
+          <t>-0.001451612903225863 +/- 0.000483870967741942</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-0.0001612903225806095 +/- 0.0009327608372525358</t>
+          <t>0.0006989247311827484 +/- 0.0006384054885504257</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>-0.004462365591397788 +/- 0.0009632512294176814</t>
+          <t>0.00032258064516125227 +/- 0.0007292827938844306</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-0.00822580645161286 +/- 0.0011290322580645147</t>
+          <t>-0.0005376344086021944 +/- 0.0007603298722435988</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-0.00021505376344084227 +/- 0.00026338599384763157</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.00021505376344084227 +/- 0.00026338599384763157</t>
+          <t>5.376344086019946e-05 +/- 0.00028952498963088585</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -3716,122 +3716,122 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.0019354838709676804 +/- 0.0010257410767924025</t>
+          <t>-0.001290322580645198 +/- 0.0007292827938844404</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.0024731182795699634 +/- 0.0015433010854201256</t>
+          <t>0.003118279569892424 +/- 0.0011226136031086517</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>-0.0002688172043010528 +/- 0.0002688172043010528</t>
+          <t>-0.00026881720430110834 +/- 0.00026881720430110834</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-0.000483870967741884 +/- 0.0005072032866696898</t>
+          <t>-0.0008064516129032584 +/- 0.0003606561254031866</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.0006989247311828484 +/- 0.0007233131208104367</t>
+          <t>-0.0005376344086022056 +/- 0.000240437416935466</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>-0.0008064516129031695 +/- 0.0008415309592741186</t>
+          <t>0.0016129032258063946 +/- 0.000899634437133419</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-0.00010752688172039892 +/- 0.0007132526430871851</t>
+          <t>-0.0005913978494624161 +/- 0.00028952498963088585</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.0010752688172043557 +/- 0.0012493494665185558</t>
+          <t>-0.0009139784946237018 +/- 0.0005913978494623899</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.0010752688172043557 +/- 0.0006361376110860116</t>
+          <t>0.0017741935483870485 +/- 0.0005913978494623697</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>-0.0003225806451612634 +/- 0.0008046575025320077</t>
+          <t>0.00043010752688167343 +/- 0.0005267719876952835</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-0.013494623655913918 +/- 0.0005613068015543306</t>
+          <t>-0.0043548387096774555 +/- 0.0007772490481075629</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>-0.017043010752688104 +/- 0.0013611816022765797</t>
+          <t>-0.0025806451612903738 +/- 0.0007901579815429461</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0008064516129032695 +/- 0.0015994058903917882</t>
+          <t>-0.0011827956989247657 +/- 0.0009249812115099574</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-0.004462365591397799 +/- 0.001129032258064508</t>
+          <t>-0.0017741935483871374 +/- 0.0006821815881961967</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-5.376344086019946e-05 +/- 0.00028952498963088585</t>
+          <t>-0.00010752688172044333 +/- 0.00021505376344088667</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>-0.0004838709677418951 +/- 0.0011888894831987046</t>
+          <t>-0.0007526881720430701 +/- 0.0005986843400892755</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>-0.014247311827956933 +/- 0.0014674563509630217</t>
+          <t>-0.0016666666666667052 +/- 0.0012824581120297399</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-0.010215053763440807 +/- 0.0004808748338709444</t>
+          <t>-0.0021505376344086446 +/- 0.0005889489865646861</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-0.012365591397849407 +/- 0.0011530973435229656</t>
+          <t>-0.004516129032258098 +/- 0.0008735525166275126</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-0.0005913978494623163 +/- 0.00037634408602147393</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2.2204460492503132e-17 +/- 0.0003400298559320905</t>
+          <t>-5.376344086022167e-05 +/- 0.000161290322580665</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>-0.0003225806451612634 +/- 0.0003566263215435616</t>
+          <t>-0.000161290322580665 +/- 0.0002463750373632475</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-0.022526881720430048 +/- 0.0022484434049813524</t>
+          <t>-0.004946236559139838 +/- 0.0008602150537634287</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-0.008064516129032218 +/- 0.0014019790118715396</t>
+          <t>-0.0015053763440860735 +/- 0.0006269840747145456</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3841,77 +3841,77 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>-0.0009139784946236018 +/- 0.00041990589655412314</t>
+          <t>-0.001451612903225874 +/- 0.00041990589655413024</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-0.007311827956989192 +/- 0.0008398117931082363</t>
+          <t>-0.0005376344086022056 +/- 0.000240437416935466</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-0.018064516129032194 +/- 0.002098840999563765</t>
+          <t>-0.003870967741935538 +/- 0.0005267719876953107</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>-0.00010752688172038782 +/- 0.0005790499792617634</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-0.004139784946236502 +/- 0.0015957873203931044</t>
+          <t>-0.0015053763440860623 +/- 0.0006269840747145436</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-0.0004301075268816623 +/- 0.0012677232389840525</t>
+          <t>-0.0011827956989247767 +/- 0.0004686988111334354</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-0.009032258064516074 +/- 0.0010144065733394328</t>
+          <t>-0.010483870967741971 +/- 0.001544237270574726</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>0.0007526881720430589 +/- 0.0009373976222668287</t>
+          <t>-0.0014516129032258519 +/- 0.0007233131208104243</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>0.00010752688172044333 +/- 0.00021505376344088667</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.00026881720430111945 +/- 0.0007697753259826052</t>
+          <t>0.001182795698924688 +/- 0.0007132526430871901</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>-0.00010752688172036562 +/- 0.001478250224179301</t>
+          <t>0.0003763440860214629 +/- 0.00041990589655411034</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.0004301075268817511 +/- 0.0005267719876953333</t>
+          <t>-0.000161290322580665 +/- 0.0002463750373632475</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0.001451612903225863 +/- 0.0008346330481860375</t>
+          <t>0.0009139784946236018 +/- 0.0004838709677419272</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>0.00032258064516133 +/- 0.0007678955299508452</t>
+          <t>0.0009677419354838235 +/- 0.0005267719876953039</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>3.3306690738754695e-17 +/- 0.00041644982217284873</t>
+          <t>0.0005913978494623163 +/- 0.00044659268080200976</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>0.00021505376344088667 +/- 0.0005482816681282803</t>
+          <t>-0.00026881720430110834 +/- 0.00026881720430110834</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>-0.0010215053763440451 +/- 0.0005613068015543305</t>
+          <t>0.00043010752688168454 +/- 0.00021505376344084227</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>-0.00010752688172042114 +/- 0.00021505376344084227</t>
+          <t>-0.00021505376344087556 +/- 0.00035662632154360844</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>0.00016129032258069831 +/- 0.0013822537776540494</t>
+          <t>-0.0005376344086021944 +/- 0.0003400298559320905</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -3951,37 +3951,37 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>-0.00037634408602147393 +/- 0.0003442539912598018</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>0.0006989247311828262 +/- 0.0009327608372525678</t>
+          <t>-3.3306690738754695e-17 +/- 0.0005376344086021501</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>0.0008602150537634801 +/- 0.0005482816681282542</t>
+          <t>5.376344086018836e-05 +/- 0.00037634408602150885</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>-0.00037634408602147393 +/- 0.0005913978494623566</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>0.0022580645161290993 +/- 0.0009855001494528677</t>
+          <t>0.0012365591397848984 +/- 0.0006821815881962195</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>0.0030107526881721024 +/- 0.0008398117931082306</t>
+          <t>0.0020967741935483454 +/- 0.0009139784946236724</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>5.376344086024387e-05 +/- 0.00037634408602151676</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-0.006132329209252307 +/- 0.0005485766017851289</t>
+          <t>0.0014523937600860349 +/- 0.0012740956731927809</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4001,27 +4001,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.0036578805809574953 +/- 0.0007136363185272431</t>
+          <t>0.0027434104357180744 +/- 0.0011895290149271718</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.00037654653039270736 +/- 0.0009332625913339079</t>
+          <t>0.00032275416890796825 +/- 0.0006888783472224644</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.0011296395911780666 +/- 0.0010049242438014854</t>
+          <t>-0.0026896180742335017 +/- 0.0013608510640853793</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.00365788058095754 +/- 0.0008263739373715601</t>
+          <t>0.0016675632060247025 +/- 0.0007776671487251766</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.00043033889187737984 +/- 0.0010971532035702624</t>
+          <t>0.0018289402904786978 +/- 0.0005485766017851203</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4031,127 +4031,127 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.0005917159763313862 +/- 0.000561608741738075</t>
+          <t>-5.3792361484705785e-05 +/- 0.0007776671487251567</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.016675632060247424 +/- 0.0013819507884524104</t>
+          <t>0.012210866057019876 +/- 0.001752178318978208</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.01231845077998921 +/- 0.0016744897704436049</t>
+          <t>0.013125336202259263 +/- 0.0017546537310704855</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.0012372243141474005 +/- 0.0006825485497821115</t>
+          <t>0.0005379236148466471 +/- 0.0012028337694996074</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.0037116729424421457 +/- 0.0006109637811511815</t>
+          <t>-0.0016137708445400855 +/- 0.0005379236148466915</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.0045185583647121995 +/- 0.0009682625067240577</t>
+          <t>0.002689618074233413 +/- 0.001250021521099763</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.006347498655190931 +/- 0.0015553342974503504</t>
+          <t>0.014093598708983279 +/- 0.0015176692823739406</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.03109198493813876 +/- 0.0016101806936090002</t>
+          <t>0.02253899946207636 +/- 0.0015673805577550665</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>-0.0024206562668101284 +/- 0.0006014168847498161</t>
+          <t>-3.3306690738754695e-17 +/- 0.001178531592265007</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.001344809037116723 +/- 0.0006014168847498061</t>
+          <t>0.0039268423883808135 +/- 0.0012278334814968858</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.00855298547606237 +/- 0.001237224314147385</t>
+          <t>0.007261968800430296 +/- 0.0012088329776355057</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.002582033351264101 +/- 0.0008936658271025429</t>
+          <t>-0.0026358257127488184 +/- 0.0009144701452393721</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>5.379236148466138e-05 +/- 0.00016137708445398413</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.0029585798816567864 +/- 0.0010277016231599015</t>
+          <t>0.0029047875201720806 +/- 0.0020582169413350206</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.0006993006993006978 +/- 0.0008350820170123762</t>
+          <t>0.0015061861215706963 +/- 0.000713636318527233</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.0026358257127487737 +/- 0.0006109637811511785</t>
+          <t>0.002205486820871394 +/- 0.0005616087417380485</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.0010220548682086882 +/- 0.00028968073195987867</t>
+          <t>-0.0015061861215707629 +/- 0.0005793614639197882</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.0034427111350188166 +/- 0.0011834319526627288</t>
+          <t>0.0027434104357180857 +/- 0.0008822603263505765</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.00010758472296932276 +/- 0.00021516944593864552</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.005433028509951565 +/- 0.001189529014927178</t>
+          <t>0.005917159763313584 +/- 0.0014434005233995308</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0.0010220548682087216 +/- 0.0011398397041644474</t>
+          <t>-0.0030123722431415366 +/- 0.000840263547703781</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>0.007154384077460996 +/- 0.0005406065422872881</t>
+          <t>0.0017213555675093862 +/- 0.0005793614639197945</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0016675632060247025 +/- 0.0006566194521642635</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.00021516944593864552 +/- 0.00026352767539352583</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.0006455083378160253 +/- 0.0004025451734022302</t>
+          <t>0.0008606777837546487 +/- 0.00035681815926364753</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -4161,107 +4161,107 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.001559978483055402 +/- 0.0006993006993006918</t>
+          <t>0.0025282409897794066 +/- 0.0007626383474318481</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.0003227541689079905 +/- 0.0009976996767612535</t>
+          <t>0.008068854222700327 +/- 0.001295491616868466</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0004841312533619746 +/- 0.00037654653039266453</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0008068854222699872 +/- 0.0006014168847497912</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.0044109736417428545 +/- 0.0005793614639197821</t>
+          <t>0.0029585798816567643 +/- 0.0007316552183289683</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>0.0055944055944055935 +/- 0.0006888783472224887</t>
+          <t>0.004572350726196839 +/- 0.0004336878831790565</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0002689618074233291 +/- 0.0004959410681706655</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.003657880580957473 +/- 0.0006718663796017645</t>
+          <t>0.0009682625067239936 +/- 0.0010149522465902725</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.003604088219472834 +/- 0.00024650756831393875</t>
+          <t>0.005917159763313562 +/- 0.0011537176218142703</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.0016137708445400523 +/- 0.0009001183717418603</t>
+          <t>0.0021516944593867105 +/- 0.0008333476807331587</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.001452393760086057 +/- 0.0022185681148253257</t>
+          <t>-4.4408920985006264e-17 +/- 0.0020270514988076265</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.002635825712748763 +/- 0.0006109637811511774</t>
+          <t>0.01032813340505644 +/- 0.0007905830261806894</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-0.0014523937600860793 +/- 0.000540606542287287</t>
+          <t>0.000645508337815992 +/- 0.0005270553507871197</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.006401291016675648 +/- 0.0008140261404207211</t>
+          <t>-0.004195804195804254 +/- 0.0007530930607853543</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.0008068854222700872 +/- 0.00036085013084990753</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0005379236148467248</t>
+          <t>0.0024744486282947233 +/- 0.0006888783472224887</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>-0.006401291016675648 +/- 0.000814026140420743</t>
+          <t>-0.005002689618074263 +/- 0.0011797585906111404</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0.0008068854222700317 +/- 0.0009081195812874667</t>
+          <t>0.007584722969338309 +/- 0.0016395643522461876</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.004464766003227516 +/- 0.0018010402412892246</t>
+          <t>0.008821947283485732 +/- 0.002570802182969015</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>0.00010758472296934496 +/- 0.00021516944593868992</t>
+          <t>0.0004303388918773243 +/- 0.0005270553507871152</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0004841312533619857 +/- 0.0005616087417380463</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.009037116729424411 +/- 0.0021082214031485197</t>
+          <t>0.004948897256589524 +/- 0.0015366171981802622</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-0.0061861215707369795 +/- 0.0009394432058403912</t>
+          <t>-0.014308768154922047 +/- 0.0009379018705843175</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4286,77 +4286,77 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>0.00037654653039268513 +/- 0.0004201317738518799</t>
+          <t>0.00010758472296931165 +/- 0.0006273213442544668</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-0.004034427111350225 +/- 0.0008419836386497666</t>
+          <t>0.0010758472296933386 +/- 0.00041667384036661153</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>0.00043033889187733544 +/- 0.0020384395181814265</t>
+          <t>-0.0029047875201721695 +/- 0.002001191526383896</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>-0.0003227541689080349 +/- 0.00035681815926364753</t>
+          <t>0.0003765465303926296 +/- 0.00024650756831388784</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.0003227541689080349 +/- 0.00026352767539358026</t>
+          <t>-5.3792361484694685e-05 +/- 0.0005616087417380613</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>0.002259279182356089 +/- 0.0014790454098835347</t>
+          <t>0.006993006993006945 +/- 0.0015214777432739164</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-0.0031199569661108486 +/- 0.0011736107708053554</t>
+          <t>0.013448090371167265 +/- 0.0019691237458550996</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>0.0036578805809574953 +/- 0.00032275416890801265</t>
+          <t>0.0018827326519633481 +/- 0.000841983638649738</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.00043033889187729104 +/- 0.00021516944593864552</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>-0.005110274341043608 +/- 0.0009081195812874602</t>
+          <t>-0.0027972027972028245 +/- 0.0011486905058667421</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>-0.004626143087681589 +/- 0.0007683085990901263</t>
+          <t>-0.004626143087681578 +/- 0.0012546426885089355</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.0012372243141473781 +/- 0.0005406065422873035</t>
+          <t>-0.0003765465303927296 +/- 0.0010220548682086988</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-0.0046799354491662394 +/- 0.0009332625913339003</t>
+          <t>0.001344809037116701 +/- 0.000551207679718097</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>-0.007100591715976346 +/- 0.0008263739373715455</t>
+          <t>-0.002582033351264168 +/- 0.0006273213442545087</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>0.001559978483055402 +/- 0.0004468329135512702</t>
+          <t>-0.0076385153308230706 +/- 0.0013132389043285515</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.0003227541689080349 +/- 0.00026352767539358026</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>0.002313071543840772 +/- 0.0006825485497821124</t>
+          <t>0.0004303388918773021 +/- 0.0003227541689079905</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>-0.0006993006993007422 +/- 0.0003444391736112556</t>
+          <t>-0.001183431952662739 +/- 0.0007136363185272448</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>-0.0015061861215707518 +/- 0.000527055350787122</t>
+          <t>0.00016137708445398413 +/- 0.0009332625913339072</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4396,37 +4396,37 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>0.00016137708445401744 +/- 0.00024650756831393875</t>
+          <t>0.00010758472296932276 +/- 0.00021516944593864552</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>-0.0010758472296934275 +/- 0.0003402127660213284</t>
+          <t>0.0005379236148466471 +/- 0.0004166738403665686</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>0.0024744486282947563 +/- 0.0006888783472224644</t>
+          <t>-0.0009144701452394099 +/- 0.0004841312533620202</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>0.00026896180742334017 +/- 0.00043368788317903586</t>
+          <t>0.0008606777837546597 +/- 0.0004303388918773576</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>5.379236148467248e-05 +/- 0.00037654653039270736</t>
+          <t>0.0009144701452393434 +/- 0.0005406065422872947</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>-0.0036578805809575287 +/- 0.0006718663796017645</t>
+          <t>0.002420656266810073 +/- 0.001027701623159916</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>-0.007261968800430363 +/- 0.0008068854222700502</t>
+          <t>-0.009090909090909127 +/- 0.0013491055625588304</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.009482257126236205 +/- 0.0008648091185176476</t>
+          <t>0.0010471204188481575 +/- 0.0009664483842836527</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4446,157 +4446,157 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.011285631180919142 +/- 0.001253092450758453</t>
+          <t>-0.006515415939499658 +/- 0.0016412723652898056</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.01297265852239673 +/- 0.0012216404886561838</t>
+          <t>-0.009656777196044197 +/- 0.0018061867011355717</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.0004072134962187279 +/- 0.0006907703366514138</t>
+          <t>-0.0006399069226294297 +/- 0.0010867679867521366</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.003723094822571227 +/- 0.0009452051663334359</t>
+          <t>-0.0004072134962187279 +/- 0.0009398193380688398</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.004770215241419418 +/- 0.000893676061415808</t>
+          <t>-0.0009307737056428067 +/- 0.0011098769068259879</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.0002326934264107017 +/- 0.0004653868528214034</t>
+          <t>5.817335660267542e-05 +/- 0.00031327311268961326</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.006806282722513113 +/- 0.0013278315544518308</t>
+          <t>0.0015706806282722475 +/- 0.0014728317511544158</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.020244328097731246 +/- 0.0027508063798806106</t>
+          <t>0.01082024432809775 +/- 0.0028403852508978845</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.020127981384525893 +/- 0.002429390694336379</t>
+          <t>0.0189645142524724 +/- 0.003272218990209462</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-0.0044211751018033655 +/- 0.0014058226845369145</t>
+          <t>-0.0002908667830133771 +/- 0.0007004999754969274</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-0.010005817335660283 +/- 0.0009307737056428067</t>
+          <t>-0.0073298429319371364 +/- 0.001543513573172989</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-0.004130308318789977 +/- 0.0012864074687316141</t>
+          <t>0.0 +/- 0.0007358412240065967</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.023152995927865027 +/- 0.003536633892628416</t>
+          <t>0.015415939499709163 +/- 0.003283060165101227</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>-0.005468295520651545 +/- 0.0017873521228315814</t>
+          <t>-0.00139616055846421 +/- 0.0011978627272817804</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>-0.003955788248981939 +/- 0.0011576351798797276</t>
+          <t>-0.005817335660267542 +/- 0.001274514386283097</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-0.010762070971495064 +/- 0.001608995542284956</t>
+          <t>0.0009307737056428178 +/- 0.0016698894816064417</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.003955788248981929 +/- 0.0008144269924374558</t>
+          <t>-0.0020360674810936397 +/- 0.0008726003490401314</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0.0009889470622454822 +/- 0.0009030933505677647</t>
+          <t>-0.011809191390343221 +/- 0.001105293775450833</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.00011634671320535084 +/- 0.0003490401396160525</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.001105293775450833 +/- 0.0016340397795448524</t>
+          <t>-0.0022687609075043415 +/- 0.000710096312724467</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>-0.005991855730075634 +/- 0.0008648091185176939</t>
+          <t>0.00017452006980802625 +/- 0.0006907703366514138</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.004479348458406007 +/- 0.0008247496729934666</t>
+          <t>-0.0003490401396160525 +/- 0.0005331676201228385</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.003199534613147148 +/- 0.0007472502954429905</t>
+          <t>0.0010471204188481575 +/- 0.0002326934264107017</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.0002908667830133771 +/- 0.0005363318474283188</t>
+          <t>0.0022687609075043636 +/- 0.001055169118511782</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.0004653868528214034 +/- 0.0003490401396160525</t>
+          <t>0.0005817335660267542 +/- 0.00045060888263029434</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.006166375799883672 +/- 0.000744982459270872</t>
+          <t>0.005642815590459626 +/- 0.001074239983282095</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0.0023269342641070168 +/- 0.001103761836009895</t>
+          <t>0.0016288539848749116 +/- 0.000893676061415769</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>0.003315881326352499 +/- 0.0013278315544517998</t>
+          <t>0.0018615474112856135 +/- 0.000569980161206086</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.002617801047120394 +/- 0.0011414436806485397</t>
+          <t>-0.0012798138452588593 +/- 0.001295582167034315</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.00017452006980802625 +/- 0.0002665838100614192</t>
+          <t>-5.817335660267542e-05 +/- 0.00017452006980802625</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.00011634671320535084 +/- 0.00023269342641070171</t>
+          <t>-0.0002326934264107017 +/- 0.000284990080603043</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -4606,272 +4606,272 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.000698080279232105 +/- 0.00139616055846421</t>
+          <t>0.0006399069226294297 +/- 0.0007562536358347805</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.014601512507271652 +/- 0.001829457265097896</t>
+          <t>0.002210587550901677 +/- 0.000726584991087668</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>-0.00011634671320535084 +/- 0.0002326934264107017</t>
+          <t>0.0004072134962187279 +/- 0.0004543484395524479</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
+          <t>0.0015706806282722364 +/- 0.00026658381006141923</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>0.0017452006980802626 +/- 0.0007804774790575108</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0.001687027341477587 +/- 0.0006607223206282978</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-0.0002908667830133771 +/- 0.0002908667830133771</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-0.0007562536358347805 +/- 0.0005846349983199996</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.0007562536358347805 +/- 0.0009030933505677648</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>-0.0023269342641070168 +/- 0.0005817335660267542</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-0.0009307737056428067 +/- 0.0008706590777833405</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>-0.0005817335660267542 +/- 0.00036792061200329834</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>0.0019778941244909753 +/- 0.0009086968791049143</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>0.004479348458406096 +/- 0.0012216404886562122</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>0.00011634671320535084 +/- 0.0003490401396160525</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>0.004013961605584704 +/- 0.0007100963127244843</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>-0.0027341477603257448 +/- 0.0008247496729934666</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>0.000698080279232105 +/- 0.0008936760614157691</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-0.001803374054682938 +/- 0.001147357936202201</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-0.000698080279232105 +/- 0.0003490401396160525</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>-0.00011634671320535084 +/- 0.00043532953889167025</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>-0.0005817335660267542 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>0.003025014543339166 +/- 0.0011865083219529792</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>-0.003897614892379253 +/- 0.0012490349362177825</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>-0.0008726003490401313 +/- 0.0005363318474283188</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>0.004363001745200745 +/- 0.001358070684110395</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>0.001512507271669583 +/- 0.0013316489985177162</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>0.00017452006980802625 +/- 0.0007381371460412682</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>0.005468295520651601 +/- 0.001014287130550467</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>-0.0012216404886561838 +/- 0.0010551691185117442</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>0.0009889470622454822 +/- 0.0007381371460412681</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>-0.0007562536358347805 +/- 0.0004543484395524479</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>0.0009889470622454822 +/- 0.0006399069226294297</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>0.0012798138452588593 +/- 0.000893676061415769</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>-0.0012798138452588593 +/- 0.0003490401396160525</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>-0.0021524141942989906 +/- 0.00093981933806884</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>0.0021524141942989906 +/- 0.0005235602094240788</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>-0.0014543339150668855 +/- 0.0003902387395287554</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>-0.0004072134962187279 +/- 0.00026658381006141923</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>-5.817335660267542e-05 +/- 0.00017452006980802625</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>0.0002908667830133771 +/- 0.0005960995209982258</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>-0.00011634671320535084 +/- 0.00023269342641070171</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>0.010005817335660283 +/- 0.001346810576240851</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>0.011343804537521818 +/- 0.0008726003490401313</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-0.0035485747527632117 +/- 0.0015269813552538382</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>0.002966841186736446 +/- 0.0006073476735840868</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.004013961605584626 +/- 0.0014118279347890405</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>-0.0005235602094240787 +/- 0.0007562536358347806</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>0.0051192553810354815 +/- 0.0013468105762408933</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>-0.0054101221640488585 +/- 0.000639906922629478</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>-0.00279232111692842 +/- 0.00139616055846421</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>0.0002326934264107017 +/- 0.0013316489985176834</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0007804774790575108</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>-0.0027341477603257556 +/- 0.0016047835048439527</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>0.004363001745200656 +/- 0.0009820792912236165</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-0.0010471204188481575 +/- 0.0011280232361643475</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>-0.0003490401396160525 +/- 0.0004653868528214034</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>-0.0009889470622454822 +/- 0.00026658381006141923</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>-0.006806282722513135 +/- 0.0003724912296354152</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>0.000698080279232105 +/- 0.0011576351798797096</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-0.003374054682955174 +/- 0.0011865083219529345</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>-0.0003490401396160525 +/- 0.0005932541609764673</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>-0.0003490401396160525 +/- 0.0004653868528214034</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>0.003723094822571238 +/- 0.0013568241756475483</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0.0008726003490401313 +/- 0.0014070257850433633</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>0.001687027341477587 +/- 0.0006073476735840868</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>-0.003606748109365887 +/- 0.0015782036028214707</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>-0.0013379872018615345 +/- 0.0003724912296354152</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>0.000698080279232105 +/- 0.00034904013961605256</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>-0.000698080279232105 +/- 0.0006784120878237632</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>-0.0002326934264107017 +/- 0.000284990080603043</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>-0.0009889470622454822 +/- 0.0007826424692887482</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>0.000698080279232105 +/- 0.0005071435652752335</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>-0.0015706806282722364 +/- 0.0006907703366514138</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>-0.0004072134962187279 +/- 0.00026658381006141923</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>-0.0004653868528214034 +/- 0.0005071435652752336</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>-0.0004653868528214034 +/- 0.00023269342641070171</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>-0.0014543339150668855 +/- 0.0007912431942254399</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>5.817335660267542e-05 +/- 0.00017452006980802625</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.00011634671320535084 +/- 0.0004353295388916703</t>
+          <t>-5.817335660267542e-05 +/- 0.0004072134962187279</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>0.0008726003490401313 +/- 0.0002908667830133771</t>
+          <t>0.00011634671320535084 +/- 0.0006265462253792266</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>0.0002326934264107017 +/- 0.0007449824592708305</t>
+          <t>5.817335660267542e-05 +/- 0.000710096312724467</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>-0.0008726003490401313 +/- 0.0005960995209982258</t>
+          <t>-0.0003490401396160525 +/- 0.0004653868528214033</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>-0.003490401396160525 +/- 0.0011634671320535084</t>
+          <t>0.0009889470622454822 +/- 0.00026658381006141923</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>-0.00017452006980802625 +/- 0.0008648091185176476</t>
+          <t>0.0012216404886561838 +/- 0.0007562536358347805</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-0.0018181818181818743 +/- 0.0008688811127952813</t>
+          <t>0.0006417112299465178 +/- 0.0005239550251942915</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4891,157 +4891,157 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.0003208556149733033 +/- 0.0011268078880056485</t>
+          <t>-0.0002673796791444194 +/- 0.0004311367779838938</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.00016042780748657393 +/- 0.0007949769383592842</t>
+          <t>-0.00010695187165776776 +/- 0.00021390374331553552</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.0006417112299465733 +/- 0.0005759534553085112</t>
+          <t>-0.0009090909090909372 +/- 0.00041766041047628283</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.00042780748663105993 +/- 0.0010641576867450443</t>
+          <t>-0.0004812834224599327 +/- 0.0007730926360856339</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0017647058823528905 +/- 0.0005374265038032424</t>
+          <t>0.00010695187165772335 +/- 0.0004001772606175378</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.00016042780748661833 +/- 0.00034241306082525896</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.0007486631016042411 +/- 0.000595482819553998</t>
+          <t>-0.0008556149732620643 +/- 0.0004901150475888405</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.010909090909090858 +/- 0.0009625668449198074</t>
+          <t>0.0025133689839572093 +/- 0.0002450575237944614</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.010855614973261974 +/- 0.0008964200328470614</t>
+          <t>0.0023529411764705577 +/- 0.00026197751259716506</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-0.0005882352941176894 +/- 0.0010814838725217678</t>
+          <t>-0.0010160427807486938 +/- 0.0003743315508021094</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>-0.0010695187165775887 +/- 0.00047830331069516644</t>
+          <t>0.00042780748663098225 +/- 0.00021390374331549112</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-0.0006951871657754239 +/- 0.0007949769383592821</t>
+          <t>0.00053475935828875 +/- 0.00033821151445651953</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.005508021390374285 +/- 0.0015872536983589083</t>
+          <t>0.0012299465240641627 +/- 0.0005882352941176369</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.00893048128342241 +/- 0.0008301697698534667</t>
+          <t>0.001978609625668426 +/- 0.0004812834224598871</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.0006951871657753572 +/- 0.000481283422459876</t>
+          <t>0.001122994652406417 +/- 0.0003743315508021444</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0.00010695187165773445 +/- 0.0004661924003786728</t>
+          <t>-0.00010695187165776776 +/- 0.00021390374331553552</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>-0.0010695187165776 +/- 0.00041422281777620456</t>
+          <t>-0.0010160427807486938 +/- 0.0003743315508021094</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>0.00032085561497322555 +/- 0.0007253828858957473</t>
+          <t>0.0010695187165775445 +/- 0.00033821151445651953</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-0.00010695187165776776 +/- 0.00021390374331553552</t>
+          <t>5.347593582887278e-05 +/- 0.00016042780748661836</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.0014973262032085932 +/- 0.0014703451427665716</t>
+          <t>-0.0016042780748663278 +/- 0.0006327358056791002</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>-0.0012299465240642182 +/- 0.0012666009927622412</t>
+          <t>0.0012834224598930466 +/- 0.00035471922891501143</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.006737967914438458 +/- 0.0008688811127952867</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.005294117647058771 +/- 0.0008092377513594238</t>
+          <t>0.00010695187165773445 +/- 0.0004661924003786983</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.003957219251336863 +/- 0.0004901150475888695</t>
+          <t>0.00016042780748661833 +/- 0.00024505752379441054</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.0004812834224599327 +/- 0.0003743315508021523</t>
+          <t>5.347593582887278e-05 +/- 0.00016042780748661833</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>0.003743315508021328 +/- 0.0016568912711047788</t>
+          <t>-0.00010695187165780107 +/- 0.0005759534553085091</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-0.00021390374331554663 +/- 0.0007253828858957588</t>
+          <t>-0.0010160427807486938 +/- 0.0002879767276542288</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>0.0002139037433154689 +/- 0.0004278074866310211</t>
+          <t>-0.000695187165775446 +/- 0.00041766041047627714</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0012299465240641183 +/- 0.00048128342245990185</t>
+          <t>0.0010695187165775445 +/- 0.00033821151445651953</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.00021390374331549112 +/- 0.00026197751259711063</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.0005882352941176782 +/- 0.0004442044846480344</t>
+          <t>5.347593582887278e-05 +/- 0.00016042780748661836</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.00042780748663097113 +/- 0.0005759534553084762</t>
+          <t>0.00016042780748660724 +/- 0.0003424130608252815</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.347593582882837e-05 +/- 0.0009400211674463522</t>
+          <t>-0.00021390374331553552 +/- 0.0005453496805981636</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -5066,202 +5066,202 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-3.3306690738754695e-17 +/- 0.0004783033106951416</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>0.0031550802139036827 +/- 0.001423906626277486</t>
+          <t>-0.0006417112299465733 +/- 0.0003208556149732589</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>0.00021390374331548 +/- 0.0004901150475888381</t>
+          <t>0.0006951871657754016 +/- 0.0006349915554565744</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>0.00021390374331548 +/- 0.0004278074866310016</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.0018716577540106472 +/- 0.0004311367779838662</t>
+          <t>0.0004278074866310044 +/- 0.0004001772606175378</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.0002139037433154689 +/- 0.0006417112299465086</t>
+          <t>0.00037433155080212054 +/- 0.0009874965407817812</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.0005882352941176117 +/- 0.000999012924720281</t>
+          <t>0.0006417112299465066 +/- 0.00046619240037868814</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.0008021390374331139 +/- 0.0012017221954140993</t>
+          <t>-0.0011764705882353122 +/- 0.0006236312187000209</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.0034759358288769414 +/- 0.000765658880389123</t>
+          <t>0.0013368983957219305 +/- 0.0002673796791443639</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-0.0003208556149733144 +/- 0.0004901150475888672</t>
+          <t>5.347593582887278e-05 +/- 0.00016042780748661836</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-0.0005347593582888277 +/- 0.0005347593582887833</t>
+          <t>-0.00016042780748666275 +/- 0.00048128342245990185</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>5.347593582887278e-05 +/- 0.00016042780748661836</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>0.0002139037433154689 +/- 0.000490115047588855</t>
+          <t>0.0002139037433155022 +/- 0.0003547192289150148</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>-0.006310160427807532 +/- 0.001618475502718879</t>
+          <t>0.00016042780748661833 +/- 0.0004176604104763013</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>0.004064171122994587 +/- 0.0013142466018657372</t>
+          <t>0.0008021390374331582 +/- 0.000358727483021378</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.0026203208556149216 +/- 0.0011331347647281673</t>
+          <t>0.00032085561497324777 +/- 0.0006848261216505907</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0.0002673796791443639 +/- 0.0002673796791443639</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0.0005347593582887278 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>0.0007486631016042633 +/- 0.0005453496805981635</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>-0.0013368983957219415 +/- 0.0004930237677696522</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>0.0002673796791443639 +/- 0.0002673796791443639</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>0.00016042780748661833 +/- 0.00024505752379441054</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>-0.00128342245989308 +/- 0.0005453496805981505</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>0.00016042780748661833 +/- 0.00024505752379441054</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>-0.00042780748663105993 +/- 0.00032085561497328106</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>-0.0006417112299465621 +/- 0.0004001772606175378</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>0.0004812834224598883 +/- 0.0004442044846480344</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>-5.347593582889498e-05 +/- 0.0002879767276542659</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>-0.0002139037433155244 +/- 0.00035471922891503485</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>-0.00048128342245992164 +/- 0.0005044909696286979</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>0.000481283422459855 +/- 0.00016042780748661836</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>-0.0009090909090909482 +/- 0.00041766041047625865</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>0.0005882352941176227 +/- 0.0002879767276542659</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>0.0007486631016042855 +/- 0.0004278074866310322</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
           <t>5.347593582887278e-05 +/- 0.00016042780748661836</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>-0.0007486631016043299 +/- 0.000800354521235086</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>-0.00010695187165776776 +/- 0.00021390374331553552</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>0.0018181818181817744 +/- 0.001224120122166804</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>0.0004278074866309933 +/- 0.0004661924003786728</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>0.00010695187165774556 +/- 0.00021390374331549115</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>-5.3475935828917186e-05 +/- 0.0007351725713833011</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>-0.0009625668449198321 +/- 0.0013055139695971715</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>-0.0011764705882353677 +/- 0.0005759534553085297</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>-0.0014438502673797204 +/- 0.0011969534377326032</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>0.001550802139037377 +/- 0.0011331347647281944</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>-0.0011764705882353454 +/- 0.000575953455308503</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>-0.000695187165775446 +/- 0.000896420032847074</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>-0.0018716577540107248 +/- 0.0009640511431721996</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>0.00048128342245986613 +/- 0.0005044909696286803</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>0.0008556149732619645 +/- 0.00026197751259711063</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>-0.0002673796791444083 +/- 0.0003587274830213779</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>-0.0034224598930481798 +/- 0.0010748530076065013</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>-0.0024064171122995413 +/- 0.0007273513641034912</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>-0.00016042780748665164 +/- 0.00024505752379446144</t>
+          <t>0.00016042780748661833 +/- 0.00024505752379441054</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5271,52 +5271,52 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>5.3475935828850575e-05 +/- 0.0003743315508021443</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>-0.0007486631016043299 +/- 0.000641711229946538</t>
+          <t>-0.0008021390374331916 +/- 0.0005978791383689351</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>-5.347593582888388e-05 +/- 0.00016042780748665164</t>
+          <t>5.347593582887278e-05 +/- 0.00016042780748661833</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>0.00016042780748659613 +/- 0.0004176604104762956</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>0.0005347593582887278 +/- 0.0004783033106951044</t>
+          <t>5.3475935828850575e-05 +/- 0.00037433155080214434</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>-0.00021390374331556883 +/- 0.0007637891367425387</t>
+          <t>5.3475935828861675e-05 +/- 0.0005583051609043176</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>5.347593582887278e-05 +/- 0.00016042780748661836</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>-0.0003208556149733033 +/- 0.0005453496805981636</t>
+          <t>0.00010695187165773445 +/- 0.00032085561497325883</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>-5.3475935828917186e-05 +/- 0.0006527569847986113</t>
+          <t>-5.347593582889498e-05 +/- 0.00044420448464802773</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>-0.0014438502673797204 +/- 0.0009874965407817926</t>
+          <t>-0.00032085561497329217 +/- 0.00035471922891503816</t>
         </is>
       </c>
     </row>
